--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -866,7 +866,7 @@
     <t>DocumentEntry.legalAuthenticator</t>
   </si>
   <si>
-    <t>y: source value from TIU DOCUMENT - VERIFIED BY (#8925-1306)</t>
+    <t>879: source value from TIU DOCUMENT - VERIFIED BY (#8925-1306)</t>
   </si>
   <si>
     <t>DocumentReference.custodian</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -677,6 +677,13 @@
     <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="clinical-note"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -705,7 +712,7 @@
     <t>DocumentEntry.class</t>
   </si>
   <si>
-    <t>875: fixed value = clinical-note</t>
+    <t>875: fixed value = #clinical-note</t>
   </si>
   <si>
     <t>DocumentReference.category:us-core</t>
@@ -1172,6 +1179,9 @@
     <t>Processors of the data need to be able to know how to interpret the data.</t>
   </si>
   <si>
+    <t>text/plain</t>
+  </si>
+  <si>
     <t>text/plain; charset=UTF-8, image/png</t>
   </si>
   <si>
@@ -1190,7 +1200,7 @@
     <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
   </si>
   <si>
-    <t>889: fixed value = text/plain</t>
+    <t>889: fixed value = #text/plain</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.language</t>
@@ -3420,7 +3430,7 @@
         <v>95</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>83</v>
@@ -4107,7 +4117,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -4122,26 +4132,26 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>208</v>
@@ -4162,13 +4172,13 @@
         <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>204</v>
@@ -4177,10 +4187,10 @@
         <v>83</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>83</v>
@@ -4191,13 +4201,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>208</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>209</v>
@@ -4257,10 +4267,10 @@
         <v>177</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4296,13 +4306,13 @@
         <v>83</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>204</v>
@@ -4311,7 +4321,7 @@
         <v>83</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>83</v>
@@ -4325,10 +4335,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4351,13 +4361,13 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4408,7 +4418,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -4423,28 +4433,28 @@
         <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AS18" t="s" s="2">
         <v>83</v>
@@ -4455,14 +4465,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4481,16 +4491,16 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4540,7 +4550,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -4555,19 +4565,19 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4576,10 +4586,10 @@
         <v>83</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AS19" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AT19" t="s" s="2">
         <v>83</v>
@@ -4587,10 +4597,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4613,16 +4623,16 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4672,7 +4682,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -4687,28 +4697,28 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AS20" t="s" s="2">
         <v>83</v>
@@ -4719,10 +4729,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4745,16 +4755,16 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4804,7 +4814,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -4819,28 +4829,28 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>83</v>
@@ -4851,10 +4861,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4877,16 +4887,16 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4936,7 +4946,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -4951,13 +4961,13 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>83</v>
@@ -4972,7 +4982,7 @@
         <v>83</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>83</v>
@@ -4983,10 +4993,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5009,16 +5019,16 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5068,7 +5078,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -5086,10 +5096,10 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>83</v>
@@ -5101,7 +5111,7 @@
         <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>83</v>
@@ -5115,10 +5125,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5141,13 +5151,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5198,7 +5208,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>84</v>
@@ -5219,7 +5229,7 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>83</v>
@@ -5245,10 +5255,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5277,7 +5287,7 @@
         <v>142</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>144</v>
@@ -5330,7 +5340,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>84</v>
@@ -5351,7 +5361,7 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>83</v>
@@ -5377,14 +5387,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5406,10 +5416,10 @@
         <v>141</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>144</v>
@@ -5464,7 +5474,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -5511,10 +5521,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5540,13 +5550,13 @@
         <v>115</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5575,10 +5585,10 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5596,7 +5606,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>95</v>
@@ -5614,10 +5624,10 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>83</v>
@@ -5629,7 +5639,7 @@
         <v>83</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>83</v>
@@ -5643,10 +5653,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5669,13 +5679,13 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5726,7 +5736,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>95</v>
@@ -5744,10 +5754,10 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>83</v>
@@ -5759,7 +5769,7 @@
         <v>83</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>83</v>
@@ -5773,10 +5783,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5799,19 +5809,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5860,7 +5870,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -5881,7 +5891,7 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>83</v>
@@ -5890,16 +5900,16 @@
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AT29" t="s" s="2">
         <v>83</v>
@@ -5907,10 +5917,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5924,7 +5934,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
@@ -5936,16 +5946,16 @@
         <v>194</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5970,13 +5980,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5994,7 +6004,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
@@ -6012,25 +6022,25 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AS30" t="s" s="2">
         <v>83</v>
@@ -6041,10 +6051,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6067,13 +6077,13 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6124,7 +6134,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>95</v>
@@ -6142,10 +6152,10 @@
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
@@ -6171,10 +6181,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6188,7 +6198,7 @@
         <v>95</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>83</v>
@@ -6197,13 +6207,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6254,7 +6264,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6275,7 +6285,7 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
@@ -6290,7 +6300,7 @@
         <v>83</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>83</v>
@@ -6301,10 +6311,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6333,7 +6343,7 @@
         <v>142</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>144</v>
@@ -6386,7 +6396,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -6407,7 +6417,7 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
@@ -6433,14 +6443,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6462,10 +6472,10 @@
         <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>144</v>
@@ -6520,7 +6530,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -6567,10 +6577,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6593,13 +6603,13 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6650,7 +6660,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>95</v>
@@ -6662,28 +6672,28 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>83</v>
@@ -6697,10 +6707,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6723,13 +6733,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6780,7 +6790,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>84</v>
@@ -6801,7 +6811,7 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>83</v>
@@ -6816,7 +6826,7 @@
         <v>83</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS36" t="s" s="2">
         <v>83</v>
@@ -6827,10 +6837,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6859,7 +6869,7 @@
         <v>142</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>144</v>
@@ -6900,19 +6910,19 @@
         <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -6933,7 +6943,7 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
@@ -6959,10 +6969,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6988,14 +6998,14 @@
         <v>115</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7005,10 +7015,10 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>83</v>
@@ -7023,10 +7033,10 @@
         <v>177</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -7044,7 +7054,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -7065,7 +7075,7 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>83</v>
@@ -7074,13 +7084,13 @@
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>83</v>
@@ -7091,10 +7101,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7108,7 +7118,7 @@
         <v>95</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -7120,14 +7130,14 @@
         <v>115</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7140,7 +7150,7 @@
         <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -7176,7 +7186,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -7197,7 +7207,7 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -7212,7 +7222,7 @@
         <v>83</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>83</v>
@@ -7223,10 +7233,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7249,19 +7259,19 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7310,7 +7320,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7319,7 +7329,7 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>107</v>
@@ -7331,7 +7341,7 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -7340,13 +7350,13 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>83</v>
@@ -7357,10 +7367,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7383,19 +7393,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7408,7 +7418,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -7444,7 +7454,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -7453,7 +7463,7 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>107</v>
@@ -7465,7 +7475,7 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -7474,7 +7484,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7491,10 +7501,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7517,19 +7527,19 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7578,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -7599,7 +7609,7 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7614,7 +7624,7 @@
         <v>83</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>83</v>
@@ -7625,10 +7635,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7651,19 +7661,19 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7712,7 +7722,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -7733,7 +7743,7 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -7748,7 +7758,7 @@
         <v>83</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>83</v>
@@ -7759,10 +7769,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7785,17 +7795,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7808,7 +7818,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7844,7 +7854,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -7865,7 +7875,7 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7880,21 +7890,21 @@
         <v>83</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7917,17 +7927,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7976,7 +7986,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -7997,7 +8007,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -8012,10 +8022,10 @@
         <v>83</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AT45" t="s" s="2">
         <v>83</v>
@@ -8023,10 +8033,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8049,16 +8059,16 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8084,11 +8094,11 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -8106,7 +8116,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>84</v>
@@ -8124,13 +8134,13 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -8139,10 +8149,10 @@
         <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AS46" t="s" s="2">
         <v>83</v>
@@ -8153,10 +8163,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8179,16 +8189,16 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8238,7 +8248,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -8259,7 +8269,7 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
@@ -8285,10 +8295,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8302,7 +8312,7 @@
         <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>83</v>
@@ -8311,13 +8321,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8368,7 +8378,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8389,7 +8399,7 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -8404,7 +8414,7 @@
         <v>83</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>83</v>
@@ -8415,10 +8425,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8447,7 +8457,7 @@
         <v>142</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>144</v>
@@ -8500,7 +8510,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8521,7 +8531,7 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
@@ -8547,14 +8557,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8576,10 +8586,10 @@
         <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>144</v>
@@ -8634,7 +8644,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -8681,10 +8691,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8707,13 +8717,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8764,7 +8774,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -8779,19 +8789,19 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8800,7 +8810,7 @@
         <v>83</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>83</v>
@@ -8811,10 +8821,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8840,13 +8850,13 @@
         <v>194</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8872,13 +8882,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8896,7 +8906,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
@@ -8914,10 +8924,10 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
@@ -8929,13 +8939,13 @@
         <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AT52" t="s" s="2">
         <v>83</v>
@@ -8943,10 +8953,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8969,13 +8979,13 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9026,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9044,13 +9054,13 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -9059,7 +9069,7 @@
         <v>83</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>83</v>
@@ -9073,10 +9083,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9099,13 +9109,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9156,7 +9166,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>84</v>
@@ -9177,7 +9187,7 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>83</v>
@@ -9203,10 +9213,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9235,7 +9245,7 @@
         <v>142</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>144</v>
@@ -9276,19 +9286,19 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -9309,7 +9319,7 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
@@ -9335,10 +9345,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9361,16 +9371,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9420,7 +9430,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>84</v>
@@ -9429,7 +9439,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9441,7 +9451,7 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>83</v>
@@ -9450,16 +9460,16 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AT56" t="s" s="2">
         <v>83</v>
@@ -9467,10 +9477,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9493,23 +9503,23 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q57" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="R57" t="s" s="2">
         <v>83</v>
@@ -9554,7 +9564,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -9563,7 +9573,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9575,7 +9585,7 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
@@ -9584,16 +9594,16 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9601,10 +9611,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9630,10 +9640,10 @@
         <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9660,13 +9670,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9684,7 +9694,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -9702,13 +9712,13 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9717,13 +9727,13 @@
         <v>83</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AT58" t="s" s="2">
         <v>83</v>
@@ -9731,10 +9741,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9760,16 +9770,16 @@
         <v>194</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9794,13 +9804,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9818,7 +9828,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -9836,13 +9846,13 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9851,10 +9861,10 @@
         <v>83</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>83</v>
@@ -9865,10 +9875,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9882,7 +9892,7 @@
         <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>83</v>
@@ -9891,13 +9901,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9948,7 +9958,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -9966,13 +9976,13 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9981,10 +9991,10 @@
         <v>83</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>83</v>
@@ -9995,10 +10005,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10012,7 +10022,7 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
@@ -10021,16 +10031,16 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10080,7 +10090,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10098,13 +10108,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -10113,10 +10123,10 @@
         <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AS61" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1318,7 +1318,7 @@
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>893: transform using null</t>
+    <t>893: transform using calculate</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.hash</t>
@@ -1342,7 +1342,7 @@
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>894: transform using null</t>
+    <t>894: transform using calculate</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.title</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -256,15 +265,6 @@
   </si>
   <si>
     <t>Mapping: XDS metadata equivalent</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t/>
@@ -508,6 +508,9 @@
     <t>The structure and format of this Id shall be consistent with the specification corresponding to the formatCode attribute. (e.g. for a DICOM standard document a 64-character numeric UID, for an HL7 CDA format a serialization of the CDA Document Id extension and root in the form "oid^extension", where OID is a 64 digits max, and the Id is a 16 UTF-8 char max. If the OID is coded without the extension then the '^' character shall not be included.).</t>
   </si>
   <si>
+    <t>870: target not supported</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -529,9 +532,6 @@
     <t>DocumentEntry.uniqueId</t>
   </si>
   <si>
-    <t>870: target not supported</t>
-  </si>
-  <si>
     <t>DocumentReference.identifier</t>
   </si>
   <si>
@@ -541,6 +541,9 @@
     <t>Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
+    <t>871: source value from TIU DOCUMENT - IEN (#8925-.001)</t>
+  </si>
+  <si>
     <t>.id / .setId</t>
   </si>
   <si>
@@ -548,9 +551,6 @@
   </si>
   <si>
     <t>DocumentEntry.entryUUID</t>
-  </si>
-  <si>
-    <t>871: source value from TIU DOCUMENT - IEN (#8925-.001)</t>
   </si>
   <si>
     <t>DocumentReference.status</t>
@@ -636,6 +636,9 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
   </si>
   <si>
+    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -656,9 +659,6 @@
   </si>
   <si>
     <t>DocumentEntry.type</t>
-  </si>
-  <si>
-    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -700,6 +700,9 @@
     <t>open</t>
   </si>
   <si>
+    <t>875: fixed value = #clinical-note</t>
+  </si>
+  <si>
     <t>Composition.class</t>
   </si>
   <si>
@@ -710,9 +713,6 @@
   </si>
   <si>
     <t>DocumentEntry.class</t>
-  </si>
-  <si>
-    <t>875: fixed value = #clinical-note</t>
   </si>
   <si>
     <t>DocumentReference.category:us-core</t>
@@ -740,6 +740,9 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
+    <t>876: source value from TIU DOCUMENT - PATIENT (#8925-.02)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -759,9 +762,6 @@
   </si>
   <si>
     <t>DocumentEntry.patientId</t>
-  </si>
-  <si>
-    <t>876: source value from TIU DOCUMENT - PATIENT (#8925-.02)</t>
   </si>
   <si>
     <t>DocumentReference.date</t>
@@ -784,6 +784,12 @@
     <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
   </si>
   <si>
+    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.EntryDateTime</t>
+  </si>
+  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -794,12 +800,6 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.EntryDateTime</t>
   </si>
   <si>
     <t>DocumentReference.author</t>
@@ -818,6 +818,9 @@
     <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
   </si>
   <si>
+    <t>1663: source value from TIU DOCUMENT - SIGNED BY (#8925-1502)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -834,9 +837,6 @@
   </si>
   <si>
     <t>DocumentEntry.author</t>
-  </si>
-  <si>
-    <t>1663: source value from TIU DOCUMENT - SIGNED BY (#8925-1502)</t>
   </si>
   <si>
     <t>DocumentReference.authenticator</t>
@@ -855,6 +855,9 @@
     <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
   </si>
   <si>
+    <t>879: source value from TIU DOCUMENT - VERIFIED BY (#8925-1306)</t>
+  </si>
+  <si>
     <t>Composition.attester</t>
   </si>
   <si>
@@ -871,9 +874,6 @@
   </si>
   <si>
     <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>879: source value from TIU DOCUMENT - VERIFIED BY (#8925-1306)</t>
   </si>
   <si>
     <t>DocumentReference.custodian</t>
@@ -892,13 +892,13 @@
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
+    <t>880: source value from TIU DOCUMENT - DIVISION (#8925-1212)</t>
+  </si>
+  <si>
     <t>Composition.custodian</t>
   </si>
   <si>
     <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
-  </si>
-  <si>
-    <t>880: source value from TIU DOCUMENT - DIVISION (#8925-1212)</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo</t>
@@ -1035,6 +1035,12 @@
     <t>Helps humans to assess whether the document is of interest.</t>
   </si>
   <si>
+    <t>885: source value from TIU DOCUMENT - SUBJECT (#8925-1701)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.DocumentSubject</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target.text</t>
   </si>
   <si>
@@ -1042,12 +1048,6 @@
   </si>
   <si>
     <t>DocumentEntry.comments</t>
-  </si>
-  <si>
-    <t>885: source value from TIU DOCUMENT - SUBJECT (#8925-1701)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.DocumentSubject</t>
   </si>
   <si>
     <t>DocumentReference.securityLabel</t>
@@ -1075,6 +1075,9 @@
     <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
+    <t>886: target not supported</t>
+  </si>
+  <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
   </si>
   <si>
@@ -1088,9 +1091,6 @@
   </si>
   <si>
     <t>DocumentEntry.confidentialityCode</t>
-  </si>
-  <si>
-    <t>886: target not supported</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1194,15 +1194,15 @@
     <t>Attachment.contentType</t>
   </si>
   <si>
+    <t>889: fixed value = #text/plain</t>
+  </si>
+  <si>
     <t>./mediaType, ./charset</t>
   </si>
   <si>
     <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
   </si>
   <si>
-    <t>889: fixed value = #text/plain</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.language</t>
   </si>
   <si>
@@ -1221,10 +1221,10 @@
     <t>Attachment.language</t>
   </si>
   <si>
+    <t>890: target not supported</t>
+  </si>
+  <si>
     <t>./language</t>
-  </si>
-  <si>
-    <t>890: target not supported</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.data</t>
@@ -1253,13 +1253,13 @@
 </t>
   </si>
   <si>
+    <t>891: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+  </si>
+  <si>
     <t>./data</t>
   </si>
   <si>
     <t>ED.5</t>
-  </si>
-  <si>
-    <t>891: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.url</t>
@@ -1315,12 +1315,12 @@
     <t>Attachment.size</t>
   </si>
   <si>
+    <t>893: transform using calculate</t>
+  </si>
+  <si>
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>893: transform using calculate</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.hash</t>
   </si>
   <si>
@@ -1339,12 +1339,12 @@
     <t>Attachment.hash</t>
   </si>
   <si>
+    <t>894: transform using calculate</t>
+  </si>
+  <si>
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>894: transform using calculate</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.title</t>
   </si>
   <si>
@@ -1363,13 +1363,13 @@
     <t>Attachment.title</t>
   </si>
   <si>
+    <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
+  </si>
+  <si>
+    <t>#ERROR_#REF!</t>
+  </si>
+  <si>
     <t>./title/data</t>
-  </si>
-  <si>
-    <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
-  </si>
-  <si>
-    <t>#ERROR_#REF!</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.creation</t>
@@ -1413,6 +1413,9 @@
     <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
   </si>
   <si>
+    <t>897: target not supported</t>
+  </si>
+  <si>
     <t>Composition.meta.profile</t>
   </si>
   <si>
@@ -1420,9 +1423,6 @@
   </si>
   <si>
     <t>DocumentEntry.formatCode</t>
-  </si>
-  <si>
-    <t>897: target not supported</t>
   </si>
   <si>
     <t>DocumentReference.context</t>
@@ -1465,6 +1465,9 @@
     <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
+    <t>899: reference from TIU DOCUMENT - VISIT (#8925-.03)</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1477,9 +1480,6 @@
     <t>FiveWs.context</t>
   </si>
   <si>
-    <t>899: reference from TIU DOCUMENT - VISIT (#8925-.03)</t>
-  </si>
-  <si>
     <t>DocumentReference.context.event</t>
   </si>
   <si>
@@ -1498,6 +1498,12 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
+    <t>900: source value from TIU DOCUMENT - VISIT TYPE (#8925-.13)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.VisitType</t>
+  </si>
+  <si>
     <t>Composition.event.code</t>
   </si>
   <si>
@@ -1505,12 +1511,6 @@
   </si>
   <si>
     <t>DocumentEntry.eventCodeList</t>
-  </si>
-  <si>
-    <t>900: source value from TIU DOCUMENT - VISIT TYPE (#8925-.13)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.VisitType</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -1567,18 +1567,18 @@
 </t>
   </si>
   <si>
+    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (#8925-.07)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.EpisodeBeginDateTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (#8925-.07)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.EpisodeBeginDateTime</t>
-  </si>
-  <si>
     <t>DocumentReference.context.period.end</t>
   </si>
   <si>
@@ -1597,18 +1597,18 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (#8925-.08)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.EpisodeEndDateTime</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
   </si>
   <si>
-    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (#8925-.08)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.EpisodeEndDateTime</t>
-  </si>
-  <si>
     <t>DocumentReference.context.facilityType</t>
   </si>
   <si>
@@ -1624,6 +1624,12 @@
     <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
   </si>
   <si>
+    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (#8925-1205 &gt; 44-2)</t>
+  </si>
+  <si>
+    <t>Dim.Location.LocationType</t>
+  </si>
+  <si>
     <t>usually from a mapping to a local ValueSet</t>
   </si>
   <si>
@@ -1636,12 +1642,6 @@
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
   </si>
   <si>
-    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (#8925-1205 &gt; 44-2)</t>
-  </si>
-  <si>
-    <t>Dim.Location.LocationType</t>
-  </si>
-  <si>
     <t>DocumentReference.context.practiceSetting</t>
   </si>
   <si>
@@ -1663,10 +1663,10 @@
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
   </si>
   <si>
+    <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (#8925-1402)</t>
+  </si>
+  <si>
     <t>DocumentEntry.practiceSettingCode</t>
-  </si>
-  <si>
-    <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (#8925-1402)</t>
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
@@ -1682,10 +1682,10 @@
     <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
   </si>
   <si>
+    <t>905: target not supported</t>
+  </si>
+  <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
-  </si>
-  <si>
-    <t>905: target not supported</t>
   </si>
   <si>
     <t>DocumentReference.context.related</t>
@@ -1704,6 +1704,9 @@
     <t>May be identifiers or resources that caused the DocumentReference or referenced Document to be created.</t>
   </si>
   <si>
+    <t>906: target not supported</t>
+  </si>
+  <si>
     <t>Composition.event.detail</t>
   </si>
   <si>
@@ -1714,9 +1717,6 @@
   </si>
   <si>
     <t>DocumentEntry.referenceIdList</t>
-  </si>
-  <si>
-    <t>906: target not supported</t>
   </si>
 </sst>
 </file>
@@ -2071,16 +2071,16 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="52.0078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="84.2265625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="162.44921875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="212.015625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="52.0078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="84.2265625" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="162.44921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2325,25 +2325,25 @@
         <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AQ2" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AR2" t="s" s="2">
         <v>83</v>
@@ -2989,16 +2989,16 @@
         <v>83</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>83</v>
@@ -3121,16 +3121,16 @@
         <v>83</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>83</v>
@@ -3253,16 +3253,16 @@
         <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>83</v>
@@ -3387,16 +3387,16 @@
         <v>83</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>83</v>
@@ -3518,31 +3518,31 @@
         <v>158</v>
       </c>
       <c r="AL11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AP11" t="s" s="2">
+      <c r="AR11" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AQ11" t="s" s="2">
+      <c r="AS11" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AR11" t="s" s="2">
+      <c r="AT11" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AS11" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT11" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3645,34 +3645,34 @@
         <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>170</v>
       </c>
       <c r="AQ12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AS12" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AR12" t="s" s="2">
+      <c r="AT12" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="AS12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT12" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
@@ -3775,34 +3775,34 @@
         <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AN13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO13" t="s" s="2">
+      <c r="AQ13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR13" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AP13" t="s" s="2">
+      <c r="AS13" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AQ13" t="s" s="2">
+      <c r="AT13" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AR13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT13" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3910,28 +3910,28 @@
         <v>83</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AS14" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR14" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS14" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AT14" t="s" s="2">
         <v>83</v>
@@ -4042,31 +4042,31 @@
         <v>200</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AP15" t="s" s="2">
+      <c r="AR15" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AQ15" t="s" s="2">
+      <c r="AS15" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AR15" t="s" s="2">
+      <c r="AT15" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AS15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT15" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -4169,34 +4169,34 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>222</v>
       </c>
       <c r="AR16" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AS16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT16" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AS16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT16" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4306,31 +4306,31 @@
         <v>83</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AS17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT17" t="s" s="2">
-        <v>83</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4436,31 +4436,31 @@
         <v>232</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AR18" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AQ18" t="s" s="2">
+      <c r="AS18" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AR18" t="s" s="2">
+      <c r="AT18" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AS18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT18" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4571,25 +4571,25 @@
         <v>247</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>249</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS19" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AT19" t="s" s="2">
         <v>83</v>
@@ -4700,31 +4700,31 @@
         <v>257</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AO20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AQ20" t="s" s="2">
+      <c r="AR20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS20" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AR20" t="s" s="2">
+      <c r="AT20" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AS20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT20" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4829,34 +4829,34 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AR21" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AQ21" t="s" s="2">
+      <c r="AS21" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AR21" t="s" s="2">
+      <c r="AT21" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AS21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT21" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4961,28 +4961,28 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP22" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>83</v>
@@ -5096,31 +5096,31 @@
         <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT23" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT23" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5229,16 +5229,16 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5361,16 +5361,16 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>83</v>
@@ -5495,16 +5495,16 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5624,31 +5624,31 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT27" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT27" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5754,31 +5754,31 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="AN28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT28" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT28" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5885,13 +5885,13 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>83</v>
@@ -5900,19 +5900,19 @@
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AR29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AS29" t="s" s="2">
+      <c r="AT29" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AT29" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -6019,34 +6019,34 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AQ30" t="s" s="2">
+      <c r="AR30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS30" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AR30" t="s" s="2">
+      <c r="AT30" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT30" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -6152,19 +6152,19 @@
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6279,28 +6279,28 @@
         <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>83</v>
@@ -6417,16 +6417,16 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6551,16 +6551,16 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6678,31 +6678,31 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP35" t="s" s="2">
+      <c r="AR35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS35" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AQ35" t="s" s="2">
+      <c r="AT35" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT35" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6805,28 +6805,28 @@
         <v>83</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="AS36" t="s" s="2">
         <v>83</v>
@@ -6943,16 +6943,16 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7069,13 +7069,13 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>83</v>
@@ -7090,10 +7090,10 @@
         <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS38" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AT38" t="s" s="2">
         <v>83</v>
@@ -7201,13 +7201,13 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>387</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -7216,13 +7216,13 @@
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>83</v>
@@ -7335,13 +7335,13 @@
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -7356,10 +7356,10 @@
         <v>83</v>
       </c>
       <c r="AR40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS40" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AT40" t="s" s="2">
         <v>83</v>
@@ -7475,25 +7475,25 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS41" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AT41" t="s" s="2">
         <v>83</v>
@@ -7603,13 +7603,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7618,13 +7618,13 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>83</v>
@@ -7737,13 +7737,13 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -7752,13 +7752,13 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>426</v>
+        <v>83</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>83</v>
@@ -7869,13 +7869,13 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>433</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7884,19 +7884,19 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT44" t="s" s="2">
-        <v>435</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -8001,13 +8001,13 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -8016,16 +8016,16 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AT45" t="s" s="2">
         <v>83</v>
@@ -8131,34 +8131,34 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>449</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>451</v>
       </c>
       <c r="AR46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT46" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT46" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8269,16 +8269,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8393,28 +8393,28 @@
         <v>83</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>83</v>
@@ -8531,16 +8531,16 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8665,16 +8665,16 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8792,19 +8792,19 @@
         <v>466</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -8921,34 +8921,34 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>83</v>
+        <v>477</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="AS52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT52" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AT52" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -9054,31 +9054,31 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AQ53" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
+      <c r="AR53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT53" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AR53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT53" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -9187,16 +9187,16 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9319,16 +9319,16 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -9445,13 +9445,13 @@
         <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>498</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>83</v>
@@ -9460,13 +9460,13 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="AS56" t="s" s="2">
         <v>501</v>
@@ -9579,13 +9579,13 @@
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
@@ -9594,13 +9594,13 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
         <v>511</v>
@@ -9709,34 +9709,34 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="AS58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT58" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AT58" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9843,34 +9843,34 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>83</v>
+        <v>530</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>518</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AR59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT59" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT59" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -9973,34 +9973,34 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>83</v>
+        <v>536</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AQ60" t="s" s="2">
-        <v>536</v>
+        <v>236</v>
       </c>
       <c r="AR60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT60" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT60" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -10105,34 +10105,34 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>83</v>
+        <v>543</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>543</v>
+        <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>546</v>
       </c>
       <c r="AR61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT61" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT61" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -675,6 +675,40 @@
   </si>
   <si>
     <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>High-level kind of a clinical document at a macro level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Composition.class</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
+  </si>
+  <si>
+    <t>DocumentEntry.class</t>
+  </si>
+  <si>
+    <t>DocumentReference.category:us-core</t>
+  </si>
+  <si>
+    <t>us-core</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -684,47 +718,13 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>The US Core DocumentReferences Type Value Set is a &amp;#39;starter set&amp;#39; of categories supported for fetching and storing clinical notes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
   </si>
   <si>
     <t>875: fixed value = #clinical-note</t>
-  </si>
-  <si>
-    <t>Composition.class</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
-  </si>
-  <si>
-    <t>DocumentEntry.class</t>
-  </si>
-  <si>
-    <t>DocumentReference.category:us-core</t>
-  </si>
-  <si>
-    <t>us-core</t>
-  </si>
-  <si>
-    <t>The US Core DocumentReferences Type Value Set is a &amp;#39;starter set&amp;#39; of categories supported for fetching and storing clinical notes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>
@@ -1315,7 +1315,7 @@
     <t>Attachment.size</t>
   </si>
   <si>
-    <t>893: transform using calculate</t>
+    <t>893: transform using calculate() on TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
   </si>
   <si>
     <t>N/A (needs data type R3 proposal)</t>
@@ -1339,7 +1339,7 @@
     <t>Attachment.hash</t>
   </si>
   <si>
-    <t>894: transform using calculate</t>
+    <t>894: transform using calculate() on TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
   </si>
   <si>
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
@@ -4117,41 +4117,41 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB16" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>208</v>
@@ -4169,25 +4169,25 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>205</v>
@@ -4196,18 +4196,18 @@
         <v>83</v>
       </c>
       <c r="AT16" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>208</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>209</v>
@@ -4249,7 +4249,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -4267,10 +4267,10 @@
         <v>177</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4303,7 +4303,7 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
@@ -4315,13 +4315,13 @@
         <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AQ17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>205</v>
@@ -4330,7 +4330,7 @@
         <v>83</v>
       </c>
       <c r="AT17" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -6919,7 +6919,7 @@
         <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>300</v>
@@ -8882,7 +8882,7 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s" s="2">
         <v>475</v>
@@ -9295,7 +9295,7 @@
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>300</v>
@@ -9670,7 +9670,7 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>515</v>
@@ -9804,7 +9804,7 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>528</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (#8925) to us-core-documentreference</t>
+    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to us-core-documentreference</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -541,7 +541,7 @@
     <t>Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
-    <t>871: source value from TIU DOCUMENT - IEN (#8925-.001)</t>
+    <t>871: source value from TIU DOCUMENT - IEN (8925-.001)</t>
   </si>
   <si>
     <t>.id / .setId</t>
@@ -636,7 +636,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
   </si>
   <si>
-    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -740,7 +740,7 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>876: source value from TIU DOCUMENT - PATIENT (#8925-.02)</t>
+    <t>876: source value from TIU DOCUMENT - PATIENT (8925-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -784,7 +784,7 @@
     <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
   </si>
   <si>
-    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
+    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EntryDateTime</t>
@@ -818,7 +818,7 @@
     <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
   </si>
   <si>
-    <t>1663: source value from TIU DOCUMENT - SIGNED BY (#8925-1502)</t>
+    <t>1663: source value from TIU DOCUMENT - SIGNED BY (8925-1502)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -855,7 +855,7 @@
     <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
   </si>
   <si>
-    <t>879: source value from TIU DOCUMENT - VERIFIED BY (#8925-1306)</t>
+    <t>879: source value from TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
   </si>
   <si>
     <t>Composition.attester</t>
@@ -892,7 +892,7 @@
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
-    <t>880: source value from TIU DOCUMENT - DIVISION (#8925-1212)</t>
+    <t>880: source value from TIU DOCUMENT - DIVISION (8925-1212)</t>
   </si>
   <si>
     <t>Composition.custodian</t>
@@ -1035,7 +1035,7 @@
     <t>Helps humans to assess whether the document is of interest.</t>
   </si>
   <si>
-    <t>885: source value from TIU DOCUMENT - SUBJECT (#8925-1701)</t>
+    <t>885: source value from TIU DOCUMENT - SUBJECT (8925-1701)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.DocumentSubject</t>
@@ -1154,7 +1154,7 @@
     <t>DocumentReference.content.attachment.id</t>
   </si>
   <si>
-    <t>888: source value from TIU DOCUMENT - IEN (#8925-.001)</t>
+    <t>888: source value from TIU DOCUMENT - IEN (8925-.001)</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.extension</t>
@@ -1253,7 +1253,7 @@
 </t>
   </si>
   <si>
-    <t>891: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+    <t>891: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>./data</t>
@@ -1315,7 +1315,7 @@
     <t>Attachment.size</t>
   </si>
   <si>
-    <t>893: transform using calculate() on TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+    <t>893: transform using calculate() on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>N/A (needs data type R3 proposal)</t>
@@ -1339,7 +1339,7 @@
     <t>Attachment.hash</t>
   </si>
   <si>
-    <t>894: transform using calculate() on TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+    <t>894: transform using calculate() on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
@@ -1363,7 +1363,7 @@
     <t>Attachment.title</t>
   </si>
   <si>
-    <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (#8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
+    <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
   </si>
   <si>
     <t>#ERROR_#REF!</t>
@@ -1391,7 +1391,7 @@
     <t>Attachment.creation</t>
   </si>
   <si>
-    <t>896: source value from TIU DOCUMENT - ENTRY DATE/TIME (#8925-1201)</t>
+    <t>896: source value from TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
   </si>
   <si>
     <t>DocumentReference.content.format</t>
@@ -1465,7 +1465,7 @@
     <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
-    <t>899: reference from TIU DOCUMENT - VISIT (#8925-.03)</t>
+    <t>899: reference from TIU DOCUMENT - VISIT (8925-.03)</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1498,7 +1498,7 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
-    <t>900: source value from TIU DOCUMENT - VISIT TYPE (#8925-.13)</t>
+    <t>900: source value from TIU DOCUMENT - VISIT TYPE (8925-.13)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.VisitType</t>
@@ -1567,7 +1567,7 @@
 </t>
   </si>
   <si>
-    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (#8925-.07)</t>
+    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (8925-.07)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EpisodeBeginDateTime</t>
@@ -1597,7 +1597,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (#8925-.08)</t>
+    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (8925-.08)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EpisodeEndDateTime</t>
@@ -1624,7 +1624,7 @@
     <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
   </si>
   <si>
-    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (#8925-1205 &gt; 44-2)</t>
+    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (8925-1205 &gt; 44-2)</t>
   </si>
   <si>
     <t>Dim.Location.LocationType</t>
@@ -1663,7 +1663,7 @@
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
   </si>
   <si>
-    <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (#8925-1402)</t>
+    <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (8925-1402)</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -2071,7 +2071,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="210.4765625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1035,7 +1035,7 @@
     <t>Helps humans to assess whether the document is of interest.</t>
   </si>
   <si>
-    <t>885: source value from TIU DOCUMENT - SUBJECT (8925-1701)</t>
+    <t>885: source value from TIU DOCUMENT - SUBJECT (OPTIONAL description) (8925-1701)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.DocumentSubject</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.TIUDocumentDefinitionIEN</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -743,6 +746,9 @@
     <t>876: source value from TIU DOCUMENT - PATIENT (8925-.02)</t>
   </si>
   <si>
+    <t>TIU.TIUDocument.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -821,6 +827,9 @@
     <t>1663: source value from TIU DOCUMENT - SIGNED BY (8925-1502)</t>
   </si>
   <si>
+    <t>TIU.TIUDocument.SignedByStaffIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -858,6 +867,9 @@
     <t>879: source value from TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
   </si>
   <si>
+    <t>TIU.TIUDocument.VerifiedByStaffIEN</t>
+  </si>
+  <si>
     <t>Composition.attester</t>
   </si>
   <si>
@@ -893,6 +905,9 @@
   </si>
   <si>
     <t>880: source value from TIU DOCUMENT - DIVISION (8925-1212)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.InstitutionIEN</t>
   </si>
   <si>
     <t>Composition.custodian</t>
@@ -1466,6 +1481,9 @@
   </si>
   <si>
     <t>899: reference from TIU DOCUMENT - VISIT (8925-.03)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1627,7 +1645,8 @@
     <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (8925-1205 &gt; 44-2)</t>
   </si>
   <si>
-    <t>Dim.Location.LocationType</t>
+    <t>TIU.TIUDocument.DocumentLocationIEN
+Dim.Location.LocationType,Dim.Location.LocationType</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -1664,6 +1683,9 @@
   </si>
   <si>
     <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (8925-1402)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.TreatingSpecialtyIEN</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -2072,7 +2094,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="210.4765625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="51.51171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="52.0078125" customWidth="true" bestFit="true"/>
@@ -4042,43 +4064,43 @@
         <v>200</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AS15" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT15" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4100,13 +4122,13 @@
         <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4132,29 +4154,29 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>84</v>
@@ -4181,36 +4203,36 @@
         <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AS16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT16" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4232,13 +4254,13 @@
         <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4249,7 +4271,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -4267,10 +4289,10 @@
         <v>177</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4288,7 +4310,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
@@ -4303,7 +4325,7 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
@@ -4315,30 +4337,30 @@
         <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AS17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4361,13 +4383,13 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4418,7 +4440,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -4433,46 +4455,46 @@
         <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AS18" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AT18" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4491,16 +4513,16 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4550,7 +4572,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -4565,28 +4587,28 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS19" t="s" s="2">
         <v>83</v>
@@ -4597,10 +4619,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4623,16 +4645,16 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4682,7 +4704,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -4697,42 +4719,42 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AT20" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4755,16 +4777,16 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4814,7 +4836,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>84</v>
@@ -4829,42 +4851,42 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AS21" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AT21" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4887,16 +4909,16 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4946,7 +4968,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -4961,22 +4983,22 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4993,10 +5015,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5019,16 +5041,16 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5078,7 +5100,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -5105,10 +5127,10 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -5120,15 +5142,15 @@
         <v>83</v>
       </c>
       <c r="AT23" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5151,13 +5173,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5208,7 +5230,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>84</v>
@@ -5238,7 +5260,7 @@
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -5255,10 +5277,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5287,7 +5309,7 @@
         <v>142</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>144</v>
@@ -5340,7 +5362,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>84</v>
@@ -5370,7 +5392,7 @@
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>83</v>
@@ -5387,14 +5409,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5416,10 +5438,10 @@
         <v>141</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>144</v>
@@ -5474,7 +5496,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -5521,10 +5543,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5550,13 +5572,13 @@
         <v>115</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5585,28 +5607,28 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>95</v>
@@ -5633,10 +5655,10 @@
         <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5648,15 +5670,15 @@
         <v>83</v>
       </c>
       <c r="AT27" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5679,13 +5701,13 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5736,7 +5758,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>95</v>
@@ -5763,10 +5785,10 @@
         <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5778,15 +5800,15 @@
         <v>83</v>
       </c>
       <c r="AT28" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5809,19 +5831,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5870,7 +5892,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -5885,10 +5907,10 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
@@ -5900,7 +5922,7 @@
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5909,18 +5931,18 @@
         <v>83</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AT29" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5946,16 +5968,16 @@
         <v>194</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5980,31 +6002,31 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
@@ -6019,7 +6041,7 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
@@ -6031,30 +6053,30 @@
         <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AT30" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6077,13 +6099,13 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6134,7 +6156,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>95</v>
@@ -6161,10 +6183,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6181,10 +6203,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6207,13 +6229,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6264,7 +6286,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6279,7 +6301,7 @@
         <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -6294,7 +6316,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6311,10 +6333,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6343,7 +6365,7 @@
         <v>142</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>144</v>
@@ -6396,7 +6418,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -6426,7 +6448,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6443,14 +6465,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6472,10 +6494,10 @@
         <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>144</v>
@@ -6530,7 +6552,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -6577,10 +6599,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6603,13 +6625,13 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6660,7 +6682,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>95</v>
@@ -6672,7 +6694,7 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6687,30 +6709,30 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AT35" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6733,13 +6755,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6790,7 +6812,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>84</v>
@@ -6805,7 +6827,7 @@
         <v>83</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -6820,7 +6842,7 @@
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6837,10 +6859,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6869,7 +6891,7 @@
         <v>142</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>144</v>
@@ -6910,19 +6932,19 @@
         <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -6952,7 +6974,7 @@
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6969,10 +6991,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6998,14 +7020,14 @@
         <v>115</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7015,10 +7037,10 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>83</v>
@@ -7033,10 +7055,10 @@
         <v>177</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -7054,7 +7076,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -7069,7 +7091,7 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
@@ -7084,7 +7106,7 @@
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
@@ -7093,7 +7115,7 @@
         <v>83</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AT38" t="s" s="2">
         <v>83</v>
@@ -7101,10 +7123,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7130,14 +7152,14 @@
         <v>115</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7150,7 +7172,7 @@
         <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -7186,7 +7208,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -7201,7 +7223,7 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -7216,7 +7238,7 @@
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -7233,10 +7255,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7259,19 +7281,19 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7320,7 +7342,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7329,13 +7351,13 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
@@ -7350,7 +7372,7 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -7359,7 +7381,7 @@
         <v>83</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AT40" t="s" s="2">
         <v>83</v>
@@ -7367,10 +7389,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7393,19 +7415,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7418,7 +7440,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -7454,7 +7476,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -7463,7 +7485,7 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>107</v>
@@ -7484,7 +7506,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7493,7 +7515,7 @@
         <v>83</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AT41" t="s" s="2">
         <v>83</v>
@@ -7501,10 +7523,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7527,19 +7549,19 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7588,7 +7610,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -7603,7 +7625,7 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
@@ -7618,7 +7640,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7635,10 +7657,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7661,19 +7683,19 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7722,7 +7744,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -7737,7 +7759,7 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
@@ -7752,7 +7774,7 @@
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>83</v>
@@ -7769,10 +7791,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7795,17 +7817,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7818,7 +7840,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7854,7 +7876,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -7869,13 +7891,13 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7884,7 +7906,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7901,10 +7923,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7927,17 +7949,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7986,7 +8008,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -8001,10 +8023,10 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>83</v>
@@ -8016,7 +8038,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -8033,10 +8055,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8059,16 +8081,16 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8094,29 +8116,29 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>84</v>
@@ -8131,7 +8153,7 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
@@ -8143,13 +8165,13 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>83</v>
@@ -8158,15 +8180,15 @@
         <v>83</v>
       </c>
       <c r="AT46" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8189,16 +8211,16 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8248,7 +8270,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -8278,7 +8300,7 @@
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8295,10 +8317,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8321,13 +8343,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8378,7 +8400,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8393,7 +8415,7 @@
         <v>83</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
@@ -8408,7 +8430,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -8425,10 +8447,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8457,7 +8479,7 @@
         <v>142</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>144</v>
@@ -8510,7 +8532,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8540,7 +8562,7 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8557,14 +8579,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8586,10 +8608,10 @@
         <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>144</v>
@@ -8644,7 +8666,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
@@ -8691,10 +8713,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8717,13 +8739,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8774,7 +8796,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -8789,28 +8811,28 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>83</v>
@@ -8821,10 +8843,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8850,13 +8872,13 @@
         <v>194</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8882,13 +8904,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8906,7 +8928,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
@@ -8921,10 +8943,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>83</v>
@@ -8933,10 +8955,10 @@
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8948,15 +8970,15 @@
         <v>83</v>
       </c>
       <c r="AT52" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8979,13 +9001,13 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9036,7 +9058,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9063,13 +9085,13 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>83</v>
@@ -9078,15 +9100,15 @@
         <v>83</v>
       </c>
       <c r="AT53" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9109,13 +9131,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9166,7 +9188,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>84</v>
@@ -9196,7 +9218,7 @@
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>83</v>
@@ -9213,10 +9235,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9245,7 +9267,7 @@
         <v>142</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>144</v>
@@ -9286,19 +9308,19 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -9328,7 +9350,7 @@
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -9345,10 +9367,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9371,16 +9393,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9430,7 +9452,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>84</v>
@@ -9439,16 +9461,16 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>83</v>
@@ -9460,7 +9482,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -9469,7 +9491,7 @@
         <v>83</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="AT56" t="s" s="2">
         <v>83</v>
@@ -9477,10 +9499,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9503,23 +9525,23 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q57" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="R57" t="s" s="2">
         <v>83</v>
@@ -9564,7 +9586,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -9573,16 +9595,16 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>83</v>
@@ -9594,7 +9616,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9603,7 +9625,7 @@
         <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9611,10 +9633,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9640,10 +9662,10 @@
         <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9670,13 +9692,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9694,7 +9716,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -9709,10 +9731,10 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>83</v>
@@ -9721,13 +9743,13 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>83</v>
@@ -9736,15 +9758,15 @@
         <v>83</v>
       </c>
       <c r="AT58" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9770,16 +9792,16 @@
         <v>194</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9804,31 +9826,31 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -9843,10 +9865,10 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>83</v>
@@ -9855,13 +9877,13 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>83</v>
@@ -9870,15 +9892,15 @@
         <v>83</v>
       </c>
       <c r="AT59" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9901,13 +9923,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9958,7 +9980,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -9973,7 +9995,7 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
@@ -9985,13 +10007,13 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>83</v>
@@ -10000,15 +10022,15 @@
         <v>83</v>
       </c>
       <c r="AT60" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10031,16 +10053,16 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10090,7 +10112,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10105,7 +10127,7 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
@@ -10117,13 +10139,13 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>83</v>
@@ -10132,7 +10154,7 @@
         <v>83</v>
       </c>
       <c r="AT61" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="607">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,6 +553,212 @@
     <t>DocumentEntry.entryUUID</t>
   </si>
   <si>
+    <t>DocumentReference.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>871-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>DocumentReference.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
     <t>DocumentReference.status</t>
   </si>
   <si>
@@ -566,9 +772,6 @@
 This element is labeled as a modifier because the status contains the codes that mark the document or reference as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/document-reference-status</t>
   </si>
   <si>
@@ -615,10 +818,6 @@
   </si>
   <si>
     <t>DocumentReference.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Kind of document (LOINC if possible)</t>
@@ -691,9 +890,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Composition.class</t>
@@ -891,10 +1087,6 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>Organization which maintains the document</t>
   </si>
   <si>
@@ -944,29 +1136,7 @@
     <t>DocumentReference.relatesTo.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DocumentReference.relatesTo.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1079,9 +1249,6 @@
   </si>
   <si>
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
@@ -1175,13 +1342,6 @@
     <t>DocumentReference.content.attachment.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
@@ -1532,10 +1692,6 @@
   </si>
   <si>
     <t>DocumentReference.context.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Time of service that is being documented</t>
@@ -2055,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT61"/>
+  <dimension ref="A1:AT69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.828125" customWidth="true" bestFit="true"/>
@@ -2077,7 +2233,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="35.69140625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -3710,32 +3866,30 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>176</v>
       </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>83</v>
@@ -3760,32 +3914,34 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Y13" s="2"/>
-      <c r="Z13" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AG13" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>95</v>
@@ -3794,7 +3950,7 @@
         <v>83</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>83</v>
@@ -3806,44 +3962,44 @@
         <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR13" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="AS13" t="s" s="2">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="AT13" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>83</v>
@@ -3852,19 +4008,19 @@
         <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3890,28 +4046,28 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>184</v>
@@ -3920,13 +4076,13 @@
         <v>84</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>83</v>
@@ -3941,19 +4097,19 @@
         <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="AS14" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="AT14" t="s" s="2">
         <v>83</v>
@@ -3961,10 +4117,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3972,33 +4128,35 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>194</v>
+        <v>115</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
       </c>
@@ -4022,13 +4180,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4061,56 +4219,56 @@
         <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AR15" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AS15" t="s" s="2">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="AT15" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="H16" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -4119,18 +4277,20 @@
         <v>96</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
       </c>
@@ -4154,35 +4314,37 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -4203,43 +4365,41 @@
         <v>83</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="AR16" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AS16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AT16" t="s" s="2">
-        <v>222</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>96</v>
@@ -4251,18 +4411,20 @@
         <v>96</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
       </c>
@@ -4271,10 +4433,10 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>83</v>
@@ -4286,13 +4448,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4310,13 +4472,13 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>83</v>
@@ -4325,7 +4487,7 @@
         <v>107</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
@@ -4337,30 +4499,30 @@
         <v>83</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AS17" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AT17" t="s" s="2">
-        <v>222</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4368,13 +4530,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4383,15 +4545,17 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -4404,7 +4568,7 @@
         <v>83</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>83</v>
@@ -4440,7 +4604,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -4455,46 +4619,46 @@
         <v>107</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="AS18" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="AT18" t="s" s="2">
-        <v>241</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4504,7 +4668,7 @@
         <v>95</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4513,17 +4677,15 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4572,7 +4734,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -4587,31 +4749,31 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>248</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="AS19" t="s" s="2">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="AT19" t="s" s="2">
         <v>83</v>
@@ -4619,10 +4781,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4633,10 +4795,10 @@
         <v>84</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>83</v>
@@ -4645,16 +4807,16 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4704,13 +4866,13 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
@@ -4719,42 +4881,42 @@
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>260</v>
+        <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS20" t="s" s="2">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="AT20" t="s" s="2">
-        <v>266</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4762,7 +4924,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>95</v>
@@ -4771,22 +4933,22 @@
         <v>96</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>268</v>
+        <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4812,13 +4974,11 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -4836,10 +4996,10 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>95</v>
@@ -4851,42 +5011,42 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>272</v>
+        <v>83</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="AS21" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="AT21" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4900,25 +5060,25 @@
         <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>281</v>
+        <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4944,13 +5104,13 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -4968,7 +5128,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -4983,31 +5143,31 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="AT22" t="s" s="2">
         <v>83</v>
@@ -5015,10 +5175,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5026,13 +5186,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>83</v>
@@ -5041,16 +5201,16 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>290</v>
+        <v>196</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5076,13 +5236,13 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -5100,13 +5260,13 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
@@ -5115,73 +5275,75 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>83</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AS23" t="s" s="2">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="AT23" t="s" s="2">
-        <v>296</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>83</v>
+        <v>275</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>298</v>
+        <v>196</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5206,43 +5368,41 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -5257,34 +5417,36 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT24" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5294,25 +5456,25 @@
         <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>142</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5323,7 +5485,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5338,13 +5500,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5362,7 +5524,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>84</v>
@@ -5374,10 +5536,10 @@
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
@@ -5389,66 +5551,62 @@
         <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT25" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>141</v>
+        <v>294</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
@@ -5496,71 +5654,71 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>138</v>
+        <v>301</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AT26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -5569,16 +5727,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>115</v>
+        <v>308</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5604,13 +5762,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5628,10 +5786,10 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>95</v>
@@ -5643,42 +5801,42 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR27" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AP27" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AS27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5686,13 +5844,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5701,15 +5859,17 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5758,13 +5918,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5773,42 +5933,42 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS28" t="s" s="2">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="AT28" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5828,23 +5988,21 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5892,7 +6050,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -5907,42 +6065,42 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AT29" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5953,32 +6111,30 @@
         <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -6002,37 +6158,37 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -6041,42 +6197,42 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AT30" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6084,13 +6240,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -6099,15 +6255,17 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6156,10 +6314,10 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>85</v>
@@ -6183,10 +6341,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6198,15 +6356,15 @@
         <v>83</v>
       </c>
       <c r="AT31" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6229,13 +6387,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>175</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>300</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6286,7 +6444,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6301,7 +6459,7 @@
         <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -6316,7 +6474,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6333,10 +6491,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6365,7 +6523,7 @@
         <v>142</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>304</v>
+        <v>180</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>144</v>
@@ -6418,7 +6576,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>184</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -6448,7 +6606,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6465,14 +6623,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>307</v>
+        <v>363</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6494,10 +6652,10 @@
         <v>141</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>308</v>
+        <v>364</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>144</v>
@@ -6552,7 +6710,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>366</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -6599,10 +6757,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6616,7 +6774,7 @@
         <v>95</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>83</v>
@@ -6625,15 +6783,17 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>361</v>
+        <v>115</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6658,13 +6818,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6682,7 +6842,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>95</v>
@@ -6694,7 +6854,7 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>364</v>
+        <v>107</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6709,30 +6869,30 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS35" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AT35" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6740,28 +6900,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>298</v>
+        <v>377</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>378</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>379</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6812,10 +6972,10 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>95</v>
@@ -6824,10 +6984,10 @@
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -6839,10 +6999,10 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6854,49 +7014,51 @@
         <v>83</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>142</v>
+        <v>384</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6932,37 +7094,37 @@
         <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>83</v>
@@ -6974,7 +7136,7 @@
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>302</v>
+        <v>390</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6983,18 +7145,18 @@
         <v>83</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AT37" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7005,10 +7167,10 @@
         <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>83</v>
@@ -7017,17 +7179,19 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7037,10 +7201,10 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>83</v>
@@ -7052,13 +7216,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -7076,13 +7240,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -7091,7 +7255,7 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
@@ -7103,30 +7267,30 @@
         <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="AT38" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7134,13 +7298,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -7149,18 +7313,16 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>115</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>389</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -7172,7 +7334,7 @@
         <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>83</v>
@@ -7184,13 +7346,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7208,13 +7370,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -7223,7 +7385,7 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -7235,10 +7397,10 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -7255,10 +7417,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7272,7 +7434,7 @@
         <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
@@ -7281,20 +7443,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>395</v>
+        <v>174</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>396</v>
+        <v>175</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -7342,7 +7500,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>400</v>
+        <v>177</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7351,13 +7509,13 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
@@ -7372,7 +7530,7 @@
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -7381,7 +7539,7 @@
         <v>83</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AT40" t="s" s="2">
         <v>83</v>
@@ -7389,46 +7547,44 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>406</v>
+        <v>141</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>142</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>180</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -7440,7 +7596,7 @@
         <v>83</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>83</v>
@@ -7476,19 +7632,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>412</v>
+        <v>184</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -7506,7 +7662,7 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>413</v>
+        <v>178</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7515,7 +7671,7 @@
         <v>83</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>414</v>
+        <v>83</v>
       </c>
       <c r="AT41" t="s" s="2">
         <v>83</v>
@@ -7523,45 +7679,45 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>364</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>365</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>419</v>
+        <v>144</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7610,22 +7766,22 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>421</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
@@ -7640,7 +7796,7 @@
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>423</v>
+        <v>138</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7657,10 +7813,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7668,7 +7824,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>95</v>
@@ -7683,20 +7839,16 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7744,10 +7896,10 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>95</v>
@@ -7756,10 +7908,10 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>107</v>
+        <v>419</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
@@ -7771,30 +7923,30 @@
         <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AT43" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7814,21 +7966,19 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>298</v>
+        <v>174</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>175</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>176</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>435</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7840,7 +7990,7 @@
         <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>83</v>
@@ -7876,7 +8026,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>437</v>
+        <v>177</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
@@ -7888,16 +8038,16 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -7906,7 +8056,7 @@
         <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>440</v>
+        <v>178</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>83</v>
@@ -7923,44 +8073,44 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>442</v>
+        <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>443</v>
+        <v>142</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7996,37 +8146,37 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>446</v>
+        <v>184</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>447</v>
+        <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>83</v>
@@ -8038,7 +8188,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>423</v>
+        <v>178</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -8055,10 +8205,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8081,18 +8231,18 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>449</v>
+        <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -8101,10 +8251,10 @@
         <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>83</v>
+        <v>431</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>83</v>
+        <v>432</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -8116,11 +8266,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -8138,7 +8290,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>84</v>
@@ -8153,7 +8305,7 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
@@ -8165,30 +8317,30 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>355</v>
+        <v>437</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="AT46" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8202,7 +8354,7 @@
         <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>83</v>
@@ -8211,18 +8363,18 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>290</v>
+        <v>115</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -8234,7 +8386,7 @@
         <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>83</v>
+        <v>443</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>83</v>
@@ -8246,13 +8398,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -8270,7 +8422,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>84</v>
@@ -8285,7 +8437,7 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
@@ -8300,7 +8452,7 @@
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8317,10 +8469,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8334,7 +8486,7 @@
         <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>83</v>
@@ -8343,16 +8495,20 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>298</v>
+        <v>448</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>299</v>
+        <v>449</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -8400,7 +8556,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>301</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8409,13 +8565,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
@@ -8430,7 +8586,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>302</v>
+        <v>456</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -8439,7 +8595,7 @@
         <v>83</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="AT48" t="s" s="2">
         <v>83</v>
@@ -8447,44 +8603,46 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>141</v>
+        <v>459</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>142</v>
+        <v>460</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>304</v>
+        <v>461</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8496,7 +8654,7 @@
         <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>83</v>
@@ -8532,19 +8690,19 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>305</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
@@ -8562,7 +8720,7 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>302</v>
+        <v>466</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>83</v>
@@ -8571,7 +8729,7 @@
         <v>83</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="AT49" t="s" s="2">
         <v>83</v>
@@ -8579,45 +8737,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>141</v>
+        <v>469</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>308</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>309</v>
+        <v>471</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>144</v>
+        <v>472</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>150</v>
+        <v>473</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8666,22 +8824,22 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>310</v>
+        <v>474</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8696,7 +8854,7 @@
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>476</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8713,10 +8871,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8736,19 +8894,23 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8796,13 +8958,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -8811,28 +8973,28 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>472</v>
+        <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>473</v>
+        <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>474</v>
+        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>83</v>
@@ -8843,10 +9005,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8857,7 +9019,7 @@
         <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>96</v>
@@ -8866,21 +9028,21 @@
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8892,7 +9054,7 @@
         <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>83</v>
@@ -8904,13 +9066,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>481</v>
+        <v>83</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>482</v>
+        <v>83</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8928,13 +9090,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8943,22 +9105,22 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>484</v>
+        <v>266</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>485</v>
+        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -8970,15 +9132,15 @@
         <v>83</v>
       </c>
       <c r="AT52" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9001,16 +9163,18 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -9058,7 +9222,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9073,10 +9237,10 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>83</v>
@@ -9085,13 +9249,13 @@
         <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>492</v>
+        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>494</v>
+        <v>83</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>83</v>
@@ -9100,15 +9264,15 @@
         <v>83</v>
       </c>
       <c r="AT53" t="s" s="2">
-        <v>495</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9122,24 +9286,26 @@
         <v>95</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>298</v>
+        <v>502</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>299</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9164,13 +9330,11 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>83</v>
+        <v>506</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -9188,7 +9352,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>84</v>
@@ -9200,10 +9364,10 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
@@ -9215,13 +9379,13 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>83</v>
+        <v>508</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>302</v>
+        <v>410</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>83</v>
+        <v>509</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>83</v>
@@ -9230,47 +9394,47 @@
         <v>83</v>
       </c>
       <c r="AT54" t="s" s="2">
-        <v>83</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>142</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>304</v>
+        <v>513</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>144</v>
+        <v>514</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9308,31 +9472,31 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>511</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -9350,7 +9514,7 @@
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>302</v>
+        <v>515</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -9367,10 +9531,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9384,26 +9548,24 @@
         <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>174</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>499</v>
+        <v>175</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9452,7 +9614,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>502</v>
+        <v>177</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>84</v>
@@ -9461,16 +9623,16 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>505</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>83</v>
@@ -9482,7 +9644,7 @@
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>506</v>
+        <v>178</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>83</v>
@@ -9491,7 +9653,7 @@
         <v>83</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="AT56" t="s" s="2">
         <v>83</v>
@@ -9499,50 +9661,48 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>442</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>509</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>510</v>
+        <v>180</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>511</v>
+        <v>144</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q57" t="s" s="2">
-        <v>512</v>
-      </c>
+      <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
         <v>83</v>
       </c>
@@ -9586,25 +9746,25 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>184</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>514</v>
+        <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>515</v>
+        <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>83</v>
@@ -9616,7 +9776,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>516</v>
+        <v>178</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9625,7 +9785,7 @@
         <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9633,42 +9793,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I58" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>194</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>519</v>
+        <v>364</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -9692,13 +9856,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>522</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9716,25 +9880,25 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>518</v>
+        <v>366</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>523</v>
+        <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>83</v>
@@ -9743,13 +9907,13 @@
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>526</v>
+        <v>138</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>527</v>
+        <v>83</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>83</v>
@@ -9758,15 +9922,15 @@
         <v>83</v>
       </c>
       <c r="AT58" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9789,20 +9953,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>194</v>
+        <v>521</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9826,13 +9986,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9850,13 +10010,13 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
@@ -9865,42 +10025,42 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT59" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9911,10 +10071,10 @@
         <v>84</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>83</v>
@@ -9923,15 +10083,17 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>540</v>
+        <v>196</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9956,13 +10118,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>535</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9980,13 +10142,13 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
@@ -9995,10 +10157,10 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>83</v>
@@ -10007,13 +10169,13 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>236</v>
+        <v>538</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>237</v>
+        <v>539</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>83</v>
@@ -10022,15 +10184,15 @@
         <v>83</v>
       </c>
       <c r="AT60" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10041,29 +10203,27 @@
         <v>84</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>546</v>
+        <v>226</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10112,13 +10272,13 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
@@ -10127,38 +10287,1092 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT61" t="s" s="2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO61" t="s" s="2">
+      <c r="B64" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AP61" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AQ61" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AR61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT61" t="s" s="2">
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>554</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS64" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AT64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q65" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="R65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AT65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT66" t="s" s="2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT67" t="s" s="2">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT68" t="s" s="2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT69" t="s" s="2">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT61">
+  <autoFilter ref="A1:AT69">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10168,7 +11382,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -679,7 +679,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>871-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>871-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -912,6 +912,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category"/&gt;
     &lt;code value="clinical-note"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -923,7 +924,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
   </si>
   <si>
-    <t>875: fixed value = #clinical-note</t>
+    <t>875: fixed value = http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category#clinical-note</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -670,7 +670,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/8925</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -679,7 +679,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>871-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>871-1: fixed value = http://va.gov/identifiers/$Sta3n/8925</t>
   </si>
   <si>
     <t>II.root or Role.id.root</t>
@@ -835,7 +835,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
   </si>
   <si>
-    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.TIUDocumentDefinitionIEN</t>
@@ -861,6 +861,194 @@
   </si>
   <si>
     <t>DocumentEntry.type</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>874-1: fixed value = http://loinc.org</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>874-2: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>DocumentReference.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>874-3: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -1571,10 +1759,6 @@
   </si>
   <si>
     <t>DocumentReference.content.format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Format/content rules for the document</t>
@@ -2212,7 +2396,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT69"/>
+  <dimension ref="A1:AT80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.828125" customWidth="true" bestFit="true"/>
@@ -2250,7 +2434,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="210.4765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="212.296875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="51.51171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -5315,36 +5499,34 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>275</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="H24" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5369,41 +5551,43 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -5418,36 +5602,34 @@
         <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>284</v>
+        <v>178</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>83</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT24" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5457,25 +5639,25 @@
         <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>142</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>180</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5486,7 +5668,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5501,31 +5683,31 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>84</v>
@@ -5537,10 +5719,10 @@
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
@@ -5552,30 +5734,30 @@
         <v>83</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>178</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>271</v>
+        <v>83</v>
       </c>
       <c r="AS25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT25" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5583,13 +5765,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -5598,16 +5780,20 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
@@ -5655,13 +5841,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -5670,46 +5856,46 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="AT26" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5719,26 +5905,24 @@
         <v>95</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>308</v>
+        <v>174</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5787,7 +5971,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>306</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -5799,31 +5983,31 @@
         <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>316</v>
+        <v>178</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="AS27" t="s" s="2">
         <v>83</v>
@@ -5834,14 +6018,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5851,25 +6035,25 @@
         <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>319</v>
+        <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>321</v>
+        <v>180</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5907,19 +6091,19 @@
         <v>83</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>184</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -5931,45 +6115,45 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>326</v>
+        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>327</v>
+        <v>178</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS28" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AT28" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5989,21 +6173,23 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>332</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -6012,7 +6198,7 @@
         <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>83</v>
@@ -6051,7 +6237,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>331</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -6066,42 +6252,42 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="AT29" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6115,25 +6301,25 @@
         <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6183,7 +6369,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
@@ -6198,22 +6384,22 @@
         <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -6222,7 +6408,7 @@
         <v>83</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="AT30" t="s" s="2">
         <v>83</v>
@@ -6230,10 +6416,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6244,10 +6430,10 @@
         <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -6256,18 +6442,18 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>353</v>
+        <v>115</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -6315,13 +6501,13 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
@@ -6330,10 +6516,10 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>83</v>
@@ -6342,10 +6528,10 @@
         <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>358</v>
+        <v>269</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6354,18 +6540,18 @@
         <v>83</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>83</v>
+        <v>310</v>
       </c>
       <c r="AT31" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6385,19 +6571,21 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>313</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -6445,7 +6633,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>177</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6457,7 +6645,7 @@
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -6475,7 +6663,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>178</v>
+        <v>316</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6484,7 +6672,7 @@
         <v>83</v>
       </c>
       <c r="AS32" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="AT32" t="s" s="2">
         <v>83</v>
@@ -6492,21 +6680,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -6515,21 +6703,23 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>319</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>142</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -6577,19 +6767,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6607,7 +6797,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>178</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6616,7 +6806,7 @@
         <v>83</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="AT33" t="s" s="2">
         <v>83</v>
@@ -6624,45 +6814,45 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>144</v>
+        <v>330</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>150</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6711,25 +6901,25 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>83</v>
@@ -6741,7 +6931,7 @@
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6750,7 +6940,7 @@
         <v>83</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AT34" t="s" s="2">
         <v>83</v>
@@ -6758,24 +6948,24 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>95</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>83</v>
@@ -6784,16 +6974,16 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6819,37 +7009,35 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>190</v>
+        <v>341</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6870,44 +7058,46 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AS35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT35" t="s" s="2">
-        <v>375</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>83</v>
@@ -6916,15 +7106,17 @@
         <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>377</v>
+        <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6934,7 +7126,7 @@
         <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>83</v>
@@ -6949,13 +7141,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6973,13 +7165,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6988,7 +7180,7 @@
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7000,30 +7192,30 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AS36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>382</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7031,7 +7223,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>95</v>
@@ -7046,20 +7238,16 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>174</v>
+        <v>356</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -7107,7 +7295,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -7122,56 +7310,56 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>83</v>
+        <v>361</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="AT37" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>83</v>
@@ -7180,20 +7368,18 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>370</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -7217,13 +7403,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -7241,13 +7427,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -7256,42 +7442,42 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AS38" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
       <c r="AT38" t="s" s="2">
-        <v>405</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7299,7 +7485,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>85</v>
@@ -7314,15 +7500,17 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7371,10 +7559,10 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>85</v>
@@ -7386,42 +7574,42 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AT39" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7435,7 +7623,7 @@
         <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
@@ -7444,15 +7632,17 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>394</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>175</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7501,7 +7691,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7513,59 +7703,59 @@
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>178</v>
+        <v>401</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="AT40" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>83</v>
@@ -7574,16 +7764,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>142</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>180</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7633,37 +7823,37 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>184</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>178</v>
+        <v>413</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7687,7 +7877,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7700,26 +7890,24 @@
         <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>141</v>
+        <v>415</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>365</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7767,7 +7955,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -7779,7 +7967,7 @@
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7794,10 +7982,10 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>138</v>
+        <v>420</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7809,15 +7997,15 @@
         <v>83</v>
       </c>
       <c r="AT42" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7825,28 +8013,28 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>174</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>175</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>176</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7897,10 +8085,10 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>177</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>95</v>
@@ -7909,7 +8097,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7924,44 +8112,44 @@
         <v>83</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>410</v>
+        <v>178</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>421</v>
+        <v>83</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="AT43" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>83</v>
@@ -7970,15 +8158,17 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -8027,22 +8217,22 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
@@ -8074,14 +8264,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>140</v>
+        <v>425</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8094,24 +8284,26 @@
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>142</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>180</v>
+        <v>427</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -8147,19 +8339,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>428</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -8189,7 +8381,7 @@
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>83</v>
@@ -8206,10 +8398,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8217,13 +8409,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>83</v>
@@ -8235,15 +8427,15 @@
         <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -8252,10 +8444,10 @@
         <v>83</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>83</v>
@@ -8291,10 +8483,10 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>95</v>
@@ -8306,42 +8498,42 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT46" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AT46" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8349,7 +8541,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>95</v>
@@ -8364,7 +8556,7 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>115</v>
+        <v>439</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>440</v>
@@ -8373,9 +8565,7 @@
         <v>441</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>442</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -8387,7 +8577,7 @@
         <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>83</v>
@@ -8399,13 +8589,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -8423,10 +8613,10 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>95</v>
@@ -8438,7 +8628,7 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
@@ -8450,10 +8640,10 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8465,15 +8655,15 @@
         <v>83</v>
       </c>
       <c r="AT47" t="s" s="2">
-        <v>83</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8493,22 +8683,22 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8557,7 +8747,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8566,16 +8756,16 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>83</v>
@@ -8587,7 +8777,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -8596,18 +8786,18 @@
         <v>83</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="AT48" t="s" s="2">
-        <v>83</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8618,10 +8808,10 @@
         <v>84</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>83</v>
@@ -8630,19 +8820,19 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8655,7 +8845,7 @@
         <v>83</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>83</v>
@@ -8667,13 +8857,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8691,22 +8881,22 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>83</v>
@@ -8718,22 +8908,22 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AP49" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS49" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AQ49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS49" t="s" s="2">
+      <c r="AT49" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AT49" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8749,10 +8939,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>96</v>
@@ -8764,20 +8954,16 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -8825,13 +9011,13 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -8840,7 +9026,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>475</v>
+        <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
@@ -8852,10 +9038,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -8872,10 +9058,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8889,29 +9075,25 @@
         <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>448</v>
+        <v>174</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>478</v>
+        <v>175</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8959,7 +9141,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>482</v>
+        <v>177</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -8971,10 +9153,10 @@
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
@@ -8989,7 +9171,7 @@
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>484</v>
+        <v>178</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>83</v>
@@ -9006,44 +9188,44 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>486</v>
+        <v>142</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -9055,7 +9237,7 @@
         <v>83</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>83</v>
@@ -9091,28 +9273,28 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>490</v>
+        <v>184</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>491</v>
+        <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>492</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
@@ -9121,7 +9303,7 @@
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>493</v>
+        <v>178</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>83</v>
@@ -9138,43 +9320,45 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>495</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>496</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>498</v>
+        <v>150</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -9223,25 +9407,25 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>499</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>83</v>
@@ -9253,7 +9437,7 @@
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>476</v>
+        <v>138</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>83</v>
@@ -9270,10 +9454,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9281,7 +9465,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>95</v>
@@ -9296,17 +9480,15 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9331,11 +9513,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>506</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -9353,10 +9537,10 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>95</v>
@@ -9365,10 +9549,10 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>107</v>
+        <v>481</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>507</v>
+        <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
@@ -9380,30 +9564,30 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>410</v>
+        <v>472</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AT54" t="s" s="2">
-        <v>510</v>
+        <v>485</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9423,20 +9607,18 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>353</v>
+        <v>174</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>512</v>
+        <v>175</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9485,7 +9667,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>511</v>
+        <v>177</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -9497,10 +9679,10 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -9515,7 +9697,7 @@
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>515</v>
+        <v>178</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>83</v>
@@ -9532,21 +9714,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -9558,15 +9740,17 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9603,34 +9787,34 @@
         <v>83</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
@@ -9662,44 +9846,44 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>142</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -9708,10 +9892,10 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>83</v>
+        <v>494</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -9723,13 +9907,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>495</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>496</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -9747,22 +9931,22 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>184</v>
+        <v>497</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9777,7 +9961,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>178</v>
+        <v>499</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9786,7 +9970,7 @@
         <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9794,45 +9978,43 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>364</v>
+        <v>502</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>150</v>
+        <v>504</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9845,7 +10027,7 @@
         <v>83</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>83</v>
@@ -9857,13 +10039,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -9881,22 +10063,22 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>83</v>
+        <v>507</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
@@ -9911,7 +10093,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>138</v>
+        <v>508</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -9928,10 +10110,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9954,16 +10136,20 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -10011,46 +10197,46 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>525</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>526</v>
+        <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>527</v>
+        <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>529</v>
+        <v>83</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="AT59" t="s" s="2">
         <v>83</v>
@@ -10058,10 +10244,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10072,7 +10258,7 @@
         <v>84</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>96</v>
@@ -10081,21 +10267,23 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>196</v>
+        <v>521</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -10107,7 +10295,7 @@
         <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>83</v>
@@ -10119,13 +10307,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>535</v>
+        <v>83</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -10143,25 +10331,25 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>536</v>
+        <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>537</v>
+        <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>83</v>
@@ -10170,10 +10358,10 @@
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10182,18 +10370,18 @@
         <v>83</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="AT60" t="s" s="2">
-        <v>540</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10216,16 +10404,20 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>226</v>
+        <v>531</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -10273,7 +10465,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10288,7 +10480,7 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>83</v>
+        <v>537</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
@@ -10300,13 +10492,13 @@
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>83</v>
@@ -10315,15 +10507,15 @@
         <v>83</v>
       </c>
       <c r="AT61" t="s" s="2">
-        <v>547</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10337,25 +10529,29 @@
         <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>174</v>
+        <v>510</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>175</v>
+        <v>540</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -10403,7 +10599,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>177</v>
+        <v>544</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10415,10 +10611,10 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>83</v>
+        <v>545</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
@@ -10433,7 +10629,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>178</v>
+        <v>546</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10450,44 +10646,44 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>142</v>
+        <v>548</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10499,7 +10695,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>83</v>
+        <v>551</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10523,40 +10719,40 @@
         <v>83</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>184</v>
+        <v>552</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>83</v>
+        <v>553</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10565,7 +10761,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>178</v>
+        <v>555</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10582,10 +10778,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10608,18 +10804,18 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>495</v>
+        <v>557</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10667,7 +10863,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10676,16 +10872,16 @@
         <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>557</v>
+        <v>375</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>83</v>
@@ -10697,7 +10893,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10706,7 +10902,7 @@
         <v>83</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>559</v>
+        <v>83</v>
       </c>
       <c r="AT64" t="s" s="2">
         <v>83</v>
@@ -10714,10 +10910,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10740,24 +10936,22 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>495</v>
+        <v>277</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>564</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>83</v>
       </c>
@@ -10777,13 +10971,11 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10801,7 +10993,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -10810,16 +11002,16 @@
         <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>555</v>
+        <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>567</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>83</v>
@@ -10828,30 +11020,30 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>568</v>
+        <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>83</v>
+        <v>570</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS65" t="s" s="2">
-        <v>569</v>
+        <v>83</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>83</v>
+        <v>571</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10871,18 +11063,20 @@
         <v>83</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>196</v>
+        <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10907,13 +11101,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>573</v>
+        <v>83</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>574</v>
+        <v>83</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10931,7 +11125,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -10946,25 +11140,25 @@
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>575</v>
+        <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AM66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>578</v>
-      </c>
       <c r="AQ66" t="s" s="2">
-        <v>579</v>
+        <v>83</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>83</v>
@@ -10973,15 +11167,15 @@
         <v>83</v>
       </c>
       <c r="AT66" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10995,7 +11189,7 @@
         <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>83</v>
@@ -11004,20 +11198,16 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>582</v>
+        <v>175</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -11041,13 +11231,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>586</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>587</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -11065,7 +11255,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>581</v>
+        <v>177</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -11077,13 +11267,13 @@
         <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>589</v>
+        <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>83</v>
@@ -11092,13 +11282,13 @@
         <v>83</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>578</v>
+        <v>178</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>577</v>
+        <v>83</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>83</v>
@@ -11107,26 +11297,26 @@
         <v>83</v>
       </c>
       <c r="AT67" t="s" s="2">
-        <v>590</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -11138,15 +11328,17 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>592</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>593</v>
+        <v>142</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11195,22 +11387,22 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>591</v>
+        <v>184</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>595</v>
+        <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
@@ -11222,13 +11414,13 @@
         <v>83</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>301</v>
+        <v>178</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>83</v>
@@ -11237,19 +11429,19 @@
         <v>83</v>
       </c>
       <c r="AT68" t="s" s="2">
-        <v>596</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11262,24 +11454,26 @@
         <v>83</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>598</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>599</v>
+        <v>426</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>600</v>
+        <v>427</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -11327,7 +11521,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>597</v>
+        <v>428</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>84</v>
@@ -11339,41 +11533,1487 @@
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AK69" t="s" s="2">
+      <c r="AK70" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AS70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT71" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO69" t="s" s="2">
+      <c r="B72" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AP69" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="AQ69" t="s" s="2">
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AR69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT69" t="s" s="2">
+      <c r="AP72" t="s" s="2">
         <v>606</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT72" t="s" s="2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT73" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT74" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS75" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AT75" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q76" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AT76" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT77" t="s" s="2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT78" t="s" s="2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT79" t="s" s="2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AR80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT80" t="s" s="2">
+        <v>667</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT69">
+  <autoFilter ref="A1:AT80">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11383,7 +13023,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1097,6 +1097,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category"/&gt;
     &lt;code value="clinical-note"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1108,7 +1109,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-category</t>
   </si>
   <si>
-    <t>875: fixed value = #clinical-note</t>
+    <t>875: fixed value = http://hl7.org/fhir/us/core/CodeSystem/us-core-documentreference-category#clinical-note</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1730,9 +1730,6 @@
     <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
   </si>
   <si>
-    <t>#ERROR_#REF!</t>
-  </si>
-  <si>
     <t>./title/data</t>
   </si>
   <si>
@@ -1988,6 +1985,10 @@
   <si>
     <t>TIU.TIUDocument.DocumentLocationIEN
 Dim.Location.LocationType,Dim.Location.LocationType</t>
+  </si>
+  <si>
+    <t>Dim.Location.LocationType
+Dim.Location.LocationType</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -10752,16 +10753,16 @@
         <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10778,10 +10779,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10804,17 +10805,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10863,7 +10864,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10878,7 +10879,7 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>375</v>
@@ -10910,10 +10911,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10939,13 +10940,13 @@
         <v>277</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10975,7 +10976,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10993,7 +10994,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11008,42 +11009,42 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT65" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT65" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11069,13 +11070,13 @@
         <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11125,7 +11126,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11155,7 +11156,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11172,10 +11173,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11270,7 +11271,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11302,10 +11303,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11434,10 +11435,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11568,10 +11569,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11594,13 +11595,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11651,7 +11652,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11666,28 +11667,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11698,10 +11699,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11727,13 +11728,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11762,11 +11763,11 @@
         <v>341</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -11783,7 +11784,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11798,42 +11799,42 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT71" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT71" t="s" s="2">
-        <v>601</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11859,10 +11860,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11913,7 +11914,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11940,30 +11941,30 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AQ72" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AQ72" t="s" s="2">
+      <c r="AR72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT72" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT72" t="s" s="2">
-        <v>608</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12090,10 +12091,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12222,10 +12223,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12248,16 +12249,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12307,7 +12308,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12316,37 +12317,37 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS75" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12354,10 +12355,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12380,68 +12381,68 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="R76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12450,37 +12451,37 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS76" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12488,10 +12489,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12517,10 +12518,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12550,11 +12551,11 @@
         <v>341</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
       </c>
@@ -12571,7 +12572,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12586,13 +12587,13 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1730,6 +1730,9 @@
     <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
   </si>
   <si>
+    <t>#ERROR_#REF!</t>
+  </si>
+  <si>
     <t>./title/data</t>
   </si>
   <si>
@@ -1812,7 +1815,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
 </t>
   </si>
   <si>
@@ -1985,10 +1988,6 @@
   <si>
     <t>TIU.TIUDocument.DocumentLocationIEN
 Dim.Location.LocationType,Dim.Location.LocationType</t>
-  </si>
-  <si>
-    <t>Dim.Location.LocationType
-Dim.Location.LocationType</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -10753,7 +10752,7 @@
         <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>554</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10762,7 +10761,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10779,10 +10778,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10805,17 +10804,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10864,7 +10863,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10879,7 +10878,7 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>375</v>
@@ -10911,10 +10910,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10940,13 +10939,13 @@
         <v>277</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10976,7 +10975,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10994,7 +10993,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11009,7 +11008,7 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -11021,13 +11020,13 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
@@ -11036,15 +11035,15 @@
         <v>83</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11070,13 +11069,13 @@
         <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11126,7 +11125,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11156,7 +11155,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11173,10 +11172,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11271,7 +11270,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11303,10 +11302,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11435,10 +11434,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11569,10 +11568,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11595,13 +11594,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11652,7 +11651,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11667,28 +11666,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11699,10 +11698,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11728,13 +11727,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11763,10 +11762,10 @@
         <v>341</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11784,7 +11783,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11799,10 +11798,10 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
@@ -11811,10 +11810,10 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11826,15 +11825,15 @@
         <v>83</v>
       </c>
       <c r="AT71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11860,10 +11859,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11914,7 +11913,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11941,13 +11940,13 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>83</v>
@@ -11956,15 +11955,15 @@
         <v>83</v>
       </c>
       <c r="AT72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12091,10 +12090,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12223,10 +12222,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12249,16 +12248,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12308,7 +12307,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12317,16 +12316,16 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
@@ -12338,7 +12337,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12347,7 +12346,7 @@
         <v>83</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12355,10 +12354,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12381,23 +12380,23 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="R76" t="s" s="2">
         <v>83</v>
@@ -12442,7 +12441,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12451,16 +12450,16 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>83</v>
@@ -12472,7 +12471,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12481,7 +12480,7 @@
         <v>83</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12489,10 +12488,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12518,10 +12517,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12551,10 +12550,10 @@
         <v>341</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -12572,7 +12571,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12587,13 +12586,13 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>637</v>
+        <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1651,6 +1651,12 @@
     <t>Attachment.url</t>
   </si>
   <si>
+    <t>892: reference from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
+  </si>
+  <si>
+    <t>#ERROR_#REF!</t>
+  </si>
+  <si>
     <t>./reference/literal</t>
   </si>
   <si>
@@ -1728,9 +1734,6 @@
   </si>
   <si>
     <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
-  </si>
-  <si>
-    <t>#ERROR_#REF!</t>
   </si>
   <si>
     <t>./title/data</t>
@@ -10346,13 +10349,13 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>83</v>
+        <v>528</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>83</v>
+        <v>529</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
@@ -10361,7 +10364,7 @@
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10370,7 +10373,7 @@
         <v>83</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10378,10 +10381,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10404,19 +10407,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10465,7 +10468,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10480,7 +10483,7 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
@@ -10495,7 +10498,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10512,10 +10515,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10541,16 +10544,16 @@
         <v>510</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10599,7 +10602,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10614,7 +10617,7 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
@@ -10629,7 +10632,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10646,10 +10649,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10675,14 +10678,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10695,7 +10698,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10731,7 +10734,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10746,13 +10749,13 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10761,7 +10764,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10778,10 +10781,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10804,17 +10807,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10863,7 +10866,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10878,7 +10881,7 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>375</v>
@@ -10893,7 +10896,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10910,10 +10913,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10939,13 +10942,13 @@
         <v>277</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10975,7 +10978,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10993,7 +10996,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11008,7 +11011,7 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -11020,13 +11023,13 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
@@ -11035,15 +11038,15 @@
         <v>83</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11069,13 +11072,13 @@
         <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11125,7 +11128,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11155,7 +11158,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11172,10 +11175,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11270,7 +11273,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11302,10 +11305,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11434,10 +11437,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11568,10 +11571,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11594,13 +11597,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11651,7 +11654,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11666,28 +11669,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11698,10 +11701,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11727,13 +11730,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11762,10 +11765,10 @@
         <v>341</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11783,7 +11786,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11798,10 +11801,10 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
@@ -11810,10 +11813,10 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11825,15 +11828,15 @@
         <v>83</v>
       </c>
       <c r="AT71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11859,10 +11862,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11913,7 +11916,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11940,13 +11943,13 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>83</v>
@@ -11955,15 +11958,15 @@
         <v>83</v>
       </c>
       <c r="AT72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12090,10 +12093,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12222,10 +12225,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12248,16 +12251,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12307,7 +12310,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12316,16 +12319,16 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
@@ -12337,7 +12340,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12346,7 +12349,7 @@
         <v>83</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12354,10 +12357,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12380,23 +12383,23 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="R76" t="s" s="2">
         <v>83</v>
@@ -12441,7 +12444,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12450,16 +12453,16 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>83</v>
@@ -12471,7 +12474,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12480,7 +12483,7 @@
         <v>83</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12488,10 +12491,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12517,10 +12520,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12550,10 +12553,10 @@
         <v>341</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -12571,7 +12574,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12586,10 +12589,10 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>83</v>
@@ -12598,13 +12601,13 @@
         <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>83</v>
@@ -12613,15 +12616,15 @@
         <v>83</v>
       </c>
       <c r="AT77" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12647,16 +12650,16 @@
         <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12684,10 +12687,10 @@
         <v>341</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12705,7 +12708,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>84</v>
@@ -12720,10 +12723,10 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>83</v>
@@ -12732,14 +12735,14 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP78" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AQ78" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="AR78" t="s" s="2">
         <v>83</v>
       </c>
@@ -12747,15 +12750,15 @@
         <v>83</v>
       </c>
       <c r="AT78" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12778,13 +12781,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12835,7 +12838,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>84</v>
@@ -12850,7 +12853,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
@@ -12877,15 +12880,15 @@
         <v>83</v>
       </c>
       <c r="AT79" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12908,16 +12911,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12967,7 +12970,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>84</v>
@@ -12982,7 +12985,7 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
@@ -12994,13 +12997,13 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>83</v>
@@ -13009,7 +13012,7 @@
         <v>83</v>
       </c>
       <c r="AT80" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1651,12 +1651,6 @@
     <t>Attachment.url</t>
   </si>
   <si>
-    <t>892: reference from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
-  </si>
-  <si>
-    <t>#ERROR_#REF!</t>
-  </si>
-  <si>
     <t>./reference/literal</t>
   </si>
   <si>
@@ -1734,6 +1728,9 @@
   </si>
   <si>
     <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
+  </si>
+  <si>
+    <t>#ERROR_#REF!</t>
   </si>
   <si>
     <t>./title/data</t>
@@ -10349,31 +10346,31 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AQ60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS60" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10381,10 +10378,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10407,19 +10404,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10468,7 +10465,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10483,7 +10480,7 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
@@ -10498,7 +10495,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10515,10 +10512,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10544,16 +10541,16 @@
         <v>510</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10602,7 +10599,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10617,7 +10614,7 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
@@ -10632,7 +10629,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10649,10 +10646,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10678,14 +10675,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10698,7 +10695,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10734,7 +10731,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10749,13 +10746,13 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10764,7 +10761,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10781,10 +10778,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10807,17 +10804,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10866,7 +10863,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10881,7 +10878,7 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>375</v>
@@ -10896,7 +10893,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10913,10 +10910,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10942,13 +10939,13 @@
         <v>277</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10978,7 +10975,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10996,7 +10993,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11011,42 +11008,42 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO65" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT65" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AR65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT65" t="s" s="2">
-        <v>572</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11072,13 +11069,13 @@
         <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11128,7 +11125,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11158,7 +11155,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11175,10 +11172,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11273,7 +11270,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11305,10 +11302,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11437,10 +11434,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11571,10 +11568,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11597,13 +11594,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11654,7 +11651,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11669,28 +11666,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11701,10 +11698,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11730,13 +11727,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11765,11 +11762,11 @@
         <v>341</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -11786,7 +11783,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11801,42 +11798,42 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AL71" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT71" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT71" t="s" s="2">
-        <v>602</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11862,10 +11859,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11916,7 +11913,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11943,30 +11940,30 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AQ72" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AQ72" t="s" s="2">
+      <c r="AR72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT72" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT72" t="s" s="2">
-        <v>609</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12093,10 +12090,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12225,10 +12222,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12251,16 +12248,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12310,7 +12307,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12319,37 +12316,37 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AM75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS75" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12357,10 +12354,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12383,68 +12380,68 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="R76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12453,37 +12450,37 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS76" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12491,10 +12488,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12520,10 +12517,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12553,11 +12550,11 @@
         <v>341</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>636</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
       </c>
@@ -12574,7 +12571,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12589,42 +12586,42 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL77" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="AM77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AP77" t="s" s="2">
+      <c r="AQ77" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AQ77" t="s" s="2">
+      <c r="AR77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT77" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT77" t="s" s="2">
-        <v>642</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12650,16 +12647,16 @@
         <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12687,11 +12684,11 @@
         <v>341</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>649</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
       </c>
@@ -12708,7 +12705,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>84</v>
@@ -12723,42 +12720,42 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT78" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT78" t="s" s="2">
-        <v>652</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12781,13 +12778,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12838,7 +12835,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>84</v>
@@ -12853,7 +12850,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
@@ -12880,15 +12877,15 @@
         <v>83</v>
       </c>
       <c r="AT79" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12911,16 +12908,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12970,7 +12967,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>84</v>
@@ -12985,34 +12982,34 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AL80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="AP80" t="s" s="2">
+      <c r="AQ80" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="AQ80" t="s" s="2">
+      <c r="AR80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT80" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="AR80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT80" t="s" s="2">
-        <v>668</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1617,9 +1617,6 @@
 </t>
   </si>
   <si>
-    <t>891: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
-  </si>
-  <si>
     <t>./data</t>
   </si>
   <si>
@@ -1651,6 +1648,12 @@
     <t>Attachment.url</t>
   </si>
   <si>
+    <t>892: transform using create(Binary)</t>
+  </si>
+  <si>
+    <t>#ERROR_#REF!</t>
+  </si>
+  <si>
     <t>./reference/literal</t>
   </si>
   <si>
@@ -1728,9 +1731,6 @@
   </si>
   <si>
     <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
-  </si>
-  <si>
-    <t>#ERROR_#REF!</t>
   </si>
   <si>
     <t>./title/data</t>
@@ -10212,31 +10212,31 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS59" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AT59" t="s" s="2">
         <v>83</v>
@@ -10244,10 +10244,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10270,19 +10270,19 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -10295,43 +10295,43 @@
         <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -10346,13 +10346,13 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>83</v>
+        <v>528</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
@@ -10361,7 +10361,7 @@
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10370,7 +10370,7 @@
         <v>83</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10378,10 +10378,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10404,19 +10404,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10465,7 +10465,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10480,7 +10480,7 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
@@ -10495,7 +10495,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10512,10 +10512,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10541,16 +10541,16 @@
         <v>510</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10599,7 +10599,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10614,7 +10614,7 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
@@ -10629,7 +10629,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10646,10 +10646,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10675,14 +10675,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10695,7 +10695,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10731,7 +10731,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10746,13 +10746,13 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>266</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10893,7 +10893,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1648,7 +1648,7 @@
     <t>Attachment.url</t>
   </si>
   <si>
-    <t>892: transform using create(Binary)</t>
+    <t>892: transform using create(Binary) on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>#ERROR_#REF!</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1815,7 +1815,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-encounter)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="675">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -841,7 +841,7 @@
     <t>TIU.TIUDocument.TIUDocumentDefinitionIEN</t>
   </si>
   <si>
-    <t>document.category,document.localTitle,document.nationalTitle,document.nationalTitleRole,document.nationalTitleService,document.nationalTitleSetting,document.nationalTitleSubject,document.nationalTitleType,document.type</t>
+    <t>Alert.Alert,Alert.AlertType,Documents.DocumentName,Documents.DocumentType,Documents.DocumentExtension.NationalTitle,Documents.DocumentExtension.NationalTitleRole,Documents.DocumentExtension.NationalTitleService,Documents.DocumentExtension.NationalTitleSetting,Documents.DocumentExtension.NationalTitleSubject,Documents.DocumentExtension.NationalTitleType,Documents.DocumentCompletionStatus.Description,Documents.VA.DocumentClass.Description,Documents.VA.NationalTitle.Description,Documents.VA.NationalTitleRole.Description,Documents.VA.NationalTitleService.Description,Documents.VA.NationalTitleSetting.Description,Documents.VA.NationalTitleSubject.Description,Documents.VA.NationalTitleType.Description,Documents.CareProvider.Description,Documents.CareProvider.Name,AdvanceDirective.Alert,AdvanceDirective.Status</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1137,6 +1137,9 @@
     <t>TIU.TIUDocument.PatientIEN</t>
   </si>
   <si>
+    <t>Documents.DocumentType</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1218,7 +1221,7 @@
     <t>TIU.TIUDocument.SignedByStaffIEN</t>
   </si>
   <si>
-    <t>document.clinician [m]</t>
+    <t>Documents.DocumentExtension.CareProviders</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1297,6 +1300,9 @@
     <t>TIU.TIUDocument.InstitutionIEN</t>
   </si>
   <si>
+    <t>Documents.EnteredAt,AdvanceDirective.EnteredAt</t>
+  </si>
+  <si>
     <t>Composition.custodian</t>
   </si>
   <si>
@@ -1421,7 +1427,7 @@
     <t>TIU.TIUDocument.DocumentSubject</t>
   </si>
   <si>
-    <t>document.subject</t>
+    <t>Documents.DocumentExtension.Subject</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target.text</t>
@@ -1660,7 +1666,7 @@
     <t>892: transform using create(Binary) on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
-    <t>document.content[n]</t>
+    <t>Alert.Comments,Documents.NoteText,AdvanceDirective.Comments</t>
   </si>
   <si>
     <t>./reference/literal</t>
@@ -1840,7 +1846,7 @@
     <t>TIU.TIUDocument.VisitIEN</t>
   </si>
   <si>
-    <t>document.encounter</t>
+    <t>Alert.EncounterNumber,Documents.EncounterNumber,AdvanceDirective.EncounterNumber</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -2002,7 +2008,7 @@
 Dim.Location.LocationType,Dim.Location.LocationType</t>
   </si>
   <si>
-    <t>document.facility</t>
+    <t>Alert.EnteredAt,Documents.DocumentExtension.PatientLocation</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -2451,7 +2457,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="212.296875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="51.51171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="211.87109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="52.0078125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -7331,40 +7337,40 @@
         <v>361</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AT37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7383,16 +7389,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7442,7 +7448,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -7457,28 +7463,28 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>83</v>
@@ -7489,10 +7495,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7515,16 +7521,16 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7574,7 +7580,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -7589,42 +7595,42 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AT39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7647,16 +7653,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7706,7 +7712,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7721,42 +7727,42 @@
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AT40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7782,13 +7788,13 @@
         <v>233</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7838,7 +7844,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -7853,22 +7859,22 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7885,10 +7891,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7911,16 +7917,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7970,7 +7976,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -7997,10 +8003,10 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -8012,15 +8018,15 @@
         <v>83</v>
       </c>
       <c r="AT42" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8147,10 +8153,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8279,14 +8285,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8308,10 +8314,10 @@
         <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>144</v>
@@ -8366,7 +8372,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -8413,10 +8419,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8442,13 +8448,13 @@
         <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8477,10 +8483,10 @@
         <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -8498,7 +8504,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8525,10 +8531,10 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -8540,15 +8546,15 @@
         <v>83</v>
       </c>
       <c r="AT46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8571,13 +8577,13 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8628,7 +8634,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>95</v>
@@ -8655,10 +8661,10 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8670,15 +8676,15 @@
         <v>83</v>
       </c>
       <c r="AT47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8704,16 +8710,16 @@
         <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8762,7 +8768,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8777,13 +8783,13 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -8792,7 +8798,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -8801,18 +8807,18 @@
         <v>83</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AT48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8838,16 +8844,16 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8875,10 +8881,10 @@
         <v>201</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8896,7 +8902,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8911,7 +8917,7 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>83</v>
@@ -8923,30 +8929,30 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AT49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8969,13 +8975,13 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9026,7 +9032,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>95</v>
@@ -9053,10 +9059,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9073,10 +9079,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9171,7 +9177,7 @@
         <v>83</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
@@ -9203,10 +9209,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9335,14 +9341,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9364,10 +9370,10 @@
         <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>144</v>
@@ -9422,7 +9428,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9469,10 +9475,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9495,13 +9501,13 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9552,7 +9558,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>95</v>
@@ -9564,7 +9570,7 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -9579,30 +9585,30 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AT54" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9697,7 +9703,7 @@
         <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -9729,10 +9735,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9861,10 +9867,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9890,14 +9896,14 @@
         <v>115</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9907,10 +9913,10 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -9925,10 +9931,10 @@
         <v>190</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -9946,7 +9952,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -9961,7 +9967,7 @@
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9976,7 +9982,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9985,7 +9991,7 @@
         <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9993,10 +9999,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10022,14 +10028,14 @@
         <v>115</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10042,7 +10048,7 @@
         <v>83</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>83</v>
@@ -10078,7 +10084,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -10093,7 +10099,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
@@ -10108,7 +10114,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -10125,10 +10131,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10151,19 +10157,19 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -10212,7 +10218,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -10221,7 +10227,7 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -10242,7 +10248,7 @@
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -10251,7 +10257,7 @@
         <v>83</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT59" t="s" s="2">
         <v>83</v>
@@ -10259,10 +10265,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10285,19 +10291,19 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -10310,7 +10316,7 @@
         <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>83</v>
@@ -10346,7 +10352,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -10355,19 +10361,19 @@
         <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
@@ -10376,7 +10382,7 @@
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10385,7 +10391,7 @@
         <v>83</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10393,10 +10399,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10419,19 +10425,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10480,7 +10486,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10495,13 +10501,13 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10510,7 +10516,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10527,10 +10533,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10553,19 +10559,19 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10614,7 +10620,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10629,13 +10635,13 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10644,7 +10650,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10661,10 +10667,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10690,14 +10696,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10710,7 +10716,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10746,7 +10752,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10761,7 +10767,7 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>266</v>
@@ -10776,7 +10782,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10793,10 +10799,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10819,17 +10825,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10878,7 +10884,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10893,10 +10899,10 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>83</v>
@@ -10908,7 +10914,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10925,10 +10931,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10954,13 +10960,13 @@
         <v>278</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10990,7 +10996,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -11008,7 +11014,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11023,7 +11029,7 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -11035,13 +11041,13 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
@@ -11050,15 +11056,15 @@
         <v>83</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11081,16 +11087,16 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11140,7 +11146,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11170,7 +11176,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11187,10 +11193,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11285,7 +11291,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11317,10 +11323,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11449,14 +11455,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11478,10 +11484,10 @@
         <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>144</v>
@@ -11536,7 +11542,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>84</v>
@@ -11583,10 +11589,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11609,13 +11615,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11666,7 +11672,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11681,28 +11687,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11713,10 +11719,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11742,13 +11748,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11777,10 +11783,10 @@
         <v>342</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11798,7 +11804,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11813,10 +11819,10 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
@@ -11825,10 +11831,10 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11840,15 +11846,15 @@
         <v>83</v>
       </c>
       <c r="AT71" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11874,10 +11880,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11928,7 +11934,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11955,13 +11961,13 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>83</v>
@@ -11970,15 +11976,15 @@
         <v>83</v>
       </c>
       <c r="AT72" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12105,10 +12111,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12237,10 +12243,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12263,16 +12269,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12322,7 +12328,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12331,16 +12337,16 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
@@ -12352,7 +12358,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12361,7 +12367,7 @@
         <v>83</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12369,10 +12375,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12395,23 +12401,23 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="R76" t="s" s="2">
         <v>83</v>
@@ -12456,7 +12462,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12465,16 +12471,16 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>83</v>
@@ -12486,7 +12492,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12495,7 +12501,7 @@
         <v>83</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12503,10 +12509,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12532,10 +12538,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12565,10 +12571,10 @@
         <v>342</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -12586,7 +12592,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12601,25 +12607,25 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>83</v>
@@ -12628,15 +12634,15 @@
         <v>83</v>
       </c>
       <c r="AT77" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12662,16 +12668,16 @@
         <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12699,10 +12705,10 @@
         <v>342</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12720,7 +12726,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>84</v>
@@ -12735,10 +12741,10 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>83</v>
@@ -12747,13 +12753,13 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>83</v>
@@ -12762,15 +12768,15 @@
         <v>83</v>
       </c>
       <c r="AT78" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12793,13 +12799,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12850,7 +12856,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>84</v>
@@ -12865,7 +12871,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
@@ -12877,13 +12883,13 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>83</v>
@@ -12892,15 +12898,15 @@
         <v>83</v>
       </c>
       <c r="AT79" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12923,16 +12929,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12982,7 +12988,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>84</v>
@@ -12997,7 +13003,7 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
@@ -13009,13 +13015,13 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>83</v>
@@ -13024,7 +13030,7 @@
         <v>83</v>
       </c>
       <c r="AT80" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -841,7 +841,7 @@
     <t>TIU.TIUDocument.TIUDocumentDefinitionIEN</t>
   </si>
   <si>
-    <t>Alert.Alert,Alert.AlertType,Documents.DocumentName,Documents.DocumentType,Documents.DocumentExtension.NationalTitle,Documents.DocumentExtension.NationalTitleRole,Documents.DocumentExtension.NationalTitleService,Documents.DocumentExtension.NationalTitleSetting,Documents.DocumentExtension.NationalTitleSubject,Documents.DocumentExtension.NationalTitleType,Documents.DocumentCompletionStatus.Description,Documents.VA.DocumentClass.Description,Documents.VA.NationalTitle.Description,Documents.VA.NationalTitleRole.Description,Documents.VA.NationalTitleService.Description,Documents.VA.NationalTitleSetting.Description,Documents.VA.NationalTitleSubject.Description,Documents.VA.NationalTitleType.Description,Documents.CareProvider.Description,Documents.CareProvider.Name,AdvanceDirective.Alert,AdvanceDirective.Status</t>
+    <t>AdvanceDirective.Alert,AdvanceDirective.Status,Alert.Alert,Alert.AlertType,Documents.DocumentName,Documents.DocumentType,Documents.Extension[DocumentExtension].NationalTitle,Documents.Extension[DocumentExtension].NationalTitleRole,Documents.Extension[DocumentExtension].NationalTitleService,Documents.Extension[DocumentExtension].NationalTitleSetting,Documents.Extension[DocumentExtension].NationalTitleSubject,Documents.Extension[DocumentExtension].NationalTitleType,Documents.DocumentCompletionStatus.Description,Documents.DocumentClass[VA.DocumentClass].Description,Documents.NationalTitle[VA.NationalTitle].Description,Documents.NationalTitleRole[VA.NationalTitleRole].Description,Documents.NationalTitleService[VA.NationalTitleService].Description,Documents.NationalTitleSetting[VA.NationalTitleSetting].Description,Documents.NationalTitleSubject[VA.NationalTitleSubject].Description,Documents.NationalTitleType[VA.NationalTitleType].Description,Documents.CareProvider.Description,Documents.CareProvider.Name</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1221,7 +1221,7 @@
     <t>TIU.TIUDocument.SignedByStaffIEN</t>
   </si>
   <si>
-    <t>Documents.DocumentExtension.CareProviders</t>
+    <t>Documents.Extension[DocumentExtension].CareProviders</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1300,7 +1300,7 @@
     <t>TIU.TIUDocument.InstitutionIEN</t>
   </si>
   <si>
-    <t>Documents.EnteredAt,AdvanceDirective.EnteredAt</t>
+    <t>AdvanceDirective.EnteredAt,Documents.EnteredAt</t>
   </si>
   <si>
     <t>Composition.custodian</t>
@@ -1427,7 +1427,7 @@
     <t>TIU.TIUDocument.DocumentSubject</t>
   </si>
   <si>
-    <t>Documents.DocumentExtension.Subject</t>
+    <t>Documents.Extension[DocumentExtension].Subject</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target.text</t>
@@ -1666,7 +1666,7 @@
     <t>892: transform using create(Binary) on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
-    <t>Alert.Comments,Documents.NoteText,AdvanceDirective.Comments</t>
+    <t>AdvanceDirective.Comments,Alert.Comments,Documents.NoteText</t>
   </si>
   <si>
     <t>./reference/literal</t>
@@ -1846,7 +1846,7 @@
     <t>TIU.TIUDocument.VisitIEN</t>
   </si>
   <si>
-    <t>Alert.EncounterNumber,Documents.EncounterNumber,AdvanceDirective.EncounterNumber</t>
+    <t>AdvanceDirective.EncounterNumber,Alert.EncounterNumber,Documents.EncounterNumber</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -2008,7 +2008,7 @@
 Dim.Location.LocationType,Dim.Location.LocationType</t>
   </si>
   <si>
-    <t>Alert.EnteredAt,Documents.DocumentExtension.PatientLocation</t>
+    <t>Alert.EnteredAt,Documents.Extension[DocumentExtension].PatientLocation</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to us-core-documentreference</t>
+    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to us-core-documentreference.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3400" uniqueCount="677">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/document-reference-status</t>
+  </si>
+  <si>
+    <t>2142: target not supported</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1630,6 +1633,9 @@
   <si>
     <t xml:space="preserve">us-core-6
 </t>
+  </si>
+  <si>
+    <t>2143: target not supported</t>
   </si>
   <si>
     <t>./data</t>
@@ -5217,7 +5223,7 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
@@ -5226,33 +5232,33 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AS21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AT21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5278,13 +5284,13 @@
         <v>115</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5313,10 +5319,10 @@
         <v>190</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -5334,7 +5340,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>84</v>
@@ -5361,19 +5367,19 @@
         <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AT22" t="s" s="2">
         <v>83</v>
@@ -5381,10 +5387,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5410,13 +5416,13 @@
         <v>196</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5445,10 +5451,10 @@
         <v>190</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -5466,7 +5472,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>84</v>
@@ -5481,42 +5487,42 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AT23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5643,10 +5649,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5775,10 +5781,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5801,19 +5807,19 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5862,7 +5868,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>84</v>
@@ -5892,7 +5898,7 @@
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5901,7 +5907,7 @@
         <v>83</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AT26" t="s" s="2">
         <v>83</v>
@@ -5909,10 +5915,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6039,10 +6045,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6171,10 +6177,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6200,16 +6206,16 @@
         <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -6219,7 +6225,7 @@
         <v>83</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>83</v>
@@ -6258,7 +6264,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -6273,7 +6279,7 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
@@ -6288,7 +6294,7 @@
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -6297,7 +6303,7 @@
         <v>83</v>
       </c>
       <c r="AS29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AT29" t="s" s="2">
         <v>83</v>
@@ -6305,10 +6311,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6334,13 +6340,13 @@
         <v>174</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6390,7 +6396,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>84</v>
@@ -6420,7 +6426,7 @@
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>83</v>
@@ -6429,7 +6435,7 @@
         <v>83</v>
       </c>
       <c r="AS30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AT30" t="s" s="2">
         <v>83</v>
@@ -6437,10 +6443,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6466,14 +6472,14 @@
         <v>115</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6522,7 +6528,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>84</v>
@@ -6537,13 +6543,13 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
@@ -6552,7 +6558,7 @@
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>83</v>
@@ -6561,7 +6567,7 @@
         <v>83</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AT31" t="s" s="2">
         <v>83</v>
@@ -6569,10 +6575,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6598,14 +6604,14 @@
         <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -6654,7 +6660,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>84</v>
@@ -6684,7 +6690,7 @@
         <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>83</v>
@@ -6693,7 +6699,7 @@
         <v>83</v>
       </c>
       <c r="AS32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AT32" t="s" s="2">
         <v>83</v>
@@ -6701,10 +6707,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6727,19 +6733,19 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6788,7 +6794,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>84</v>
@@ -6818,7 +6824,7 @@
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>83</v>
@@ -6827,7 +6833,7 @@
         <v>83</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AT33" t="s" s="2">
         <v>83</v>
@@ -6835,10 +6841,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6864,16 +6870,16 @@
         <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6922,7 +6928,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -6937,13 +6943,13 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
@@ -6952,7 +6958,7 @@
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6961,7 +6967,7 @@
         <v>83</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AT34" t="s" s="2">
         <v>83</v>
@@ -6969,14 +6975,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6998,13 +7004,13 @@
         <v>196</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7030,19 +7036,19 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -7052,7 +7058,7 @@
         <v>183</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -7079,36 +7085,36 @@
         <v>83</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7130,13 +7136,13 @@
         <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7147,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>83</v>
@@ -7165,10 +7171,10 @@
         <v>190</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -7186,7 +7192,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>84</v>
@@ -7201,7 +7207,7 @@
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7213,30 +7219,30 @@
         <v>83</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7259,13 +7265,13 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7316,7 +7322,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>84</v>
@@ -7331,46 +7337,46 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AT37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7389,16 +7395,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7448,7 +7454,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>84</v>
@@ -7463,28 +7469,28 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>83</v>
@@ -7495,10 +7501,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7521,16 +7527,16 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7580,7 +7586,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -7595,42 +7601,42 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AT39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7653,16 +7659,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7712,7 +7718,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7727,42 +7733,42 @@
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AT40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7788,13 +7794,13 @@
         <v>233</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7844,7 +7850,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -7859,22 +7865,22 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7891,10 +7897,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7917,16 +7923,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7976,7 +7982,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -8003,10 +8009,10 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -8018,15 +8024,15 @@
         <v>83</v>
       </c>
       <c r="AT42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8153,10 +8159,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8285,14 +8291,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8314,10 +8320,10 @@
         <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>144</v>
@@ -8372,7 +8378,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -8419,10 +8425,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8448,13 +8454,13 @@
         <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8483,10 +8489,10 @@
         <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -8504,7 +8510,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8531,10 +8537,10 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -8546,15 +8552,15 @@
         <v>83</v>
       </c>
       <c r="AT46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8577,13 +8583,13 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8634,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>95</v>
@@ -8661,10 +8667,10 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8676,15 +8682,15 @@
         <v>83</v>
       </c>
       <c r="AT47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8710,16 +8716,16 @@
         <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8768,7 +8774,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8783,13 +8789,13 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -8798,7 +8804,7 @@
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>83</v>
@@ -8807,18 +8813,18 @@
         <v>83</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AT48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8844,16 +8850,16 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8881,10 +8887,10 @@
         <v>201</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8902,7 +8908,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8917,7 +8923,7 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>83</v>
@@ -8929,30 +8935,30 @@
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AT49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8975,13 +8981,13 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9032,7 +9038,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>95</v>
@@ -9059,10 +9065,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9079,10 +9085,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9177,7 +9183,7 @@
         <v>83</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
@@ -9209,10 +9215,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9341,14 +9347,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9370,10 +9376,10 @@
         <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>144</v>
@@ -9428,7 +9434,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9475,10 +9481,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9501,13 +9507,13 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9558,7 +9564,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>95</v>
@@ -9570,7 +9576,7 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -9585,30 +9591,30 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AT54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9703,7 +9709,7 @@
         <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -9735,10 +9741,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9867,10 +9873,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9896,14 +9902,14 @@
         <v>115</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9913,10 +9919,10 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -9931,10 +9937,10 @@
         <v>190</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -9952,7 +9958,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -9967,7 +9973,7 @@
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9982,7 +9988,7 @@
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>83</v>
@@ -9991,7 +9997,7 @@
         <v>83</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -9999,10 +10005,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10028,14 +10034,14 @@
         <v>115</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10048,7 +10054,7 @@
         <v>83</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>83</v>
@@ -10084,7 +10090,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -10099,7 +10105,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>83</v>
@@ -10114,7 +10120,7 @@
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -10131,10 +10137,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10157,19 +10163,19 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -10218,7 +10224,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -10227,13 +10233,13 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>83</v>
+        <v>523</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>83</v>
@@ -10248,7 +10254,7 @@
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>83</v>
@@ -10257,7 +10263,7 @@
         <v>83</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AT59" t="s" s="2">
         <v>83</v>
@@ -10265,10 +10271,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10291,19 +10297,19 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -10316,7 +10322,7 @@
         <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>83</v>
@@ -10352,7 +10358,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -10361,19 +10367,19 @@
         <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
@@ -10382,7 +10388,7 @@
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>83</v>
@@ -10391,7 +10397,7 @@
         <v>83</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10399,10 +10405,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10425,19 +10431,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10486,7 +10492,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10501,13 +10507,13 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10516,7 +10522,7 @@
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10533,10 +10539,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10559,19 +10565,19 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10620,7 +10626,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10635,13 +10641,13 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -10650,7 +10656,7 @@
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10667,10 +10673,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10696,14 +10702,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10716,7 +10722,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10752,7 +10758,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10767,13 +10773,13 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
@@ -10782,7 +10788,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10799,10 +10805,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10825,17 +10831,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10884,7 +10890,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10899,10 +10905,10 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>83</v>
@@ -10914,7 +10920,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -10931,10 +10937,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10957,16 +10963,16 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10996,7 +11002,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -11014,7 +11020,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>84</v>
@@ -11029,7 +11035,7 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -11041,13 +11047,13 @@
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>83</v>
@@ -11056,15 +11062,15 @@
         <v>83</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11087,16 +11093,16 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11146,7 +11152,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>84</v>
@@ -11176,7 +11182,7 @@
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>83</v>
@@ -11193,10 +11199,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11291,7 +11297,7 @@
         <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -11323,10 +11329,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11455,14 +11461,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11484,10 +11490,10 @@
         <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>144</v>
@@ -11542,7 +11548,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>84</v>
@@ -11589,10 +11595,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11615,13 +11621,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11672,7 +11678,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>84</v>
@@ -11687,28 +11693,28 @@
         <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>83</v>
@@ -11719,10 +11725,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11748,13 +11754,13 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11780,13 +11786,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11804,7 +11810,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -11819,10 +11825,10 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>83</v>
@@ -11831,10 +11837,10 @@
         <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -11846,15 +11852,15 @@
         <v>83</v>
       </c>
       <c r="AT71" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11880,10 +11886,10 @@
         <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11934,7 +11940,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>84</v>
@@ -11961,13 +11967,13 @@
         <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>83</v>
@@ -11976,15 +11982,15 @@
         <v>83</v>
       </c>
       <c r="AT72" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12111,10 +12117,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12243,10 +12249,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12269,16 +12275,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12328,7 +12334,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>84</v>
@@ -12337,16 +12343,16 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>83</v>
@@ -12358,7 +12364,7 @@
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>83</v>
@@ -12367,7 +12373,7 @@
         <v>83</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AT75" t="s" s="2">
         <v>83</v>
@@ -12375,10 +12381,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12401,23 +12407,23 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q76" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="R76" t="s" s="2">
         <v>83</v>
@@ -12462,7 +12468,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -12471,16 +12477,16 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>83</v>
@@ -12492,7 +12498,7 @@
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>83</v>
@@ -12501,7 +12507,7 @@
         <v>83</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AT76" t="s" s="2">
         <v>83</v>
@@ -12509,10 +12515,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12538,10 +12544,10 @@
         <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12568,13 +12574,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -12592,7 +12598,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -12607,25 +12613,25 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>83</v>
@@ -12634,15 +12640,15 @@
         <v>83</v>
       </c>
       <c r="AT77" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12668,16 +12674,16 @@
         <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12702,13 +12708,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12726,7 +12732,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>84</v>
@@ -12741,10 +12747,10 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>83</v>
@@ -12753,13 +12759,13 @@
         <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>83</v>
@@ -12768,15 +12774,15 @@
         <v>83</v>
       </c>
       <c r="AT78" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12799,13 +12805,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12856,7 +12862,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>84</v>
@@ -12871,7 +12877,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>83</v>
@@ -12883,13 +12889,13 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>83</v>
@@ -12898,15 +12904,15 @@
         <v>83</v>
       </c>
       <c r="AT79" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12929,16 +12935,16 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12988,7 +12994,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>84</v>
@@ -13003,7 +13009,7 @@
         <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
@@ -13015,13 +13021,13 @@
         <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>83</v>
@@ -13030,7 +13036,7 @@
         <v>83</v>
       </c>
       <c r="AT80" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,7 +541,7 @@
     <t>Other identifiers associated with the document, including version independent identifiers.</t>
   </si>
   <si>
-    <t>871: source value from TIU DOCUMENT - IEN (8925-.001)</t>
+    <t>871: source value based on TIU DOCUMENT - IEN (8925-.001)</t>
   </si>
   <si>
     <t>.id / .setId</t>
@@ -838,7 +838,7 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-documentreference-type</t>
   </si>
   <si>
-    <t>874: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1)</t>
+    <t>874: source value based on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.TIUDocumentDefinitionIEN</t>
@@ -975,7 +975,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>874-2: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2)</t>
+    <t>874-2: source value based on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - CODING SYSTEM (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-2)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1048,7 +1048,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>874-3: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
+    <t>874-3: source value based on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - DOCUMENT TYPE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.08)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1134,7 +1134,7 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>876: source value from TIU DOCUMENT - PATIENT (8925-.02)</t>
+    <t>876: source value based on TIU DOCUMENT - PATIENT (8925-.02)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.PatientIEN</t>
@@ -1184,7 +1184,7 @@
     <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
   </si>
   <si>
-    <t>877: source value from TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
+    <t>877: source value based on TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EntryDateTime</t>
@@ -1218,7 +1218,7 @@
     <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
   </si>
   <si>
-    <t>1663: source value from TIU DOCUMENT - SIGNED BY (8925-1502)</t>
+    <t>1663: source value based on TIU DOCUMENT - SIGNED BY (8925-1502)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.SignedByStaffIEN</t>
@@ -1261,7 +1261,7 @@
     <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
   </si>
   <si>
-    <t>879: source value from TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
+    <t>879: source value based on TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.VerifiedByStaffIEN</t>
@@ -1297,7 +1297,7 @@
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
-    <t>880: source value from TIU DOCUMENT - DIVISION (8925-1212)</t>
+    <t>880: source value based on TIU DOCUMENT - DIVISION (8925-1212)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.InstitutionIEN</t>
@@ -1424,7 +1424,7 @@
     <t>Helps humans to assess whether the document is of interest.</t>
   </si>
   <si>
-    <t>885: source value from TIU DOCUMENT - SUBJECT (OPTIONAL description) (8925-1701)</t>
+    <t>885: source value based on TIU DOCUMENT - SUBJECT (OPTIONAL description) (8925-1701)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.DocumentSubject</t>
@@ -1543,7 +1543,7 @@
     <t>DocumentReference.content.attachment.id</t>
   </si>
   <si>
-    <t>888: source value from TIU DOCUMENT - IEN (8925-.001)</t>
+    <t>888: source value based on TIU DOCUMENT - IEN (8925-.001)</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.extension</t>
@@ -1751,7 +1751,7 @@
     <t>Attachment.title</t>
   </si>
   <si>
-    <t>895: source value from TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
+    <t>895: source value based on TIU DOCUMENT - DOCUMENT TYPE &gt; TIU DOCUMENT DEFINITION - VHA ENTERPRISE STANDARD TITLE &gt; TIU VHA ENTERPRISE STANDARD TITLE - STANDARD TITLE (8925-.01 &gt; 8925.1-1501 &gt; 8926.1-.01)</t>
   </si>
   <si>
     <t>./title/data</t>
@@ -1776,7 +1776,7 @@
     <t>Attachment.creation</t>
   </si>
   <si>
-    <t>896: source value from TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
+    <t>896: source value based on TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
   </si>
   <si>
     <t>DocumentReference.content.format</t>
@@ -1846,7 +1846,7 @@
     <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
-    <t>899: reference from TIU DOCUMENT - VISIT (8925-.03)</t>
+    <t>899: reference based on TIU DOCUMENT - VISIT (8925-.03)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.VisitIEN</t>
@@ -1885,7 +1885,7 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
-    <t>900: source value from TIU DOCUMENT - VISIT TYPE (8925-.13)</t>
+    <t>900: source value based on TIU DOCUMENT - VISIT TYPE (8925-.13)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.VisitType</t>
@@ -1950,7 +1950,7 @@
 </t>
   </si>
   <si>
-    <t>901: source value from TIU DOCUMENT - EPISODE BEGIN DATE/TIME (8925-.07)</t>
+    <t>901: source value based on TIU DOCUMENT - EPISODE BEGIN DATE/TIME (8925-.07)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EpisodeBeginDateTime</t>
@@ -1980,7 +1980,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>902: source value from TIU DOCUMENT - EPISODE END DATE/TIME (8925-.08)</t>
+    <t>902: source value based on TIU DOCUMENT - EPISODE END DATE/TIME (8925-.08)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.EpisodeEndDateTime</t>
@@ -2007,7 +2007,7 @@
     <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
   </si>
   <si>
-    <t>903: source value from TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (8925-1205 &gt; 44-2)</t>
+    <t>903: source value based on TIU DOCUMENT - HOSPITAL LOCATION &gt; HOSPITAL LOCATION - TYPE (8925-1205 &gt; 44-2)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.DocumentLocationIEN
@@ -2050,7 +2050,7 @@
     <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
   </si>
   <si>
-    <t>904: source value from TIU DOCUMENT - TREATING SPECIALTY (8925-1402)</t>
+    <t>904: source value based on TIU DOCUMENT - TREATING SPECIALTY (8925-1402)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.TreatingSpecialtyIEN</t>
@@ -2461,7 +2461,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="212.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="216.390625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="51.51171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1124,7 +1124,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1134,7 +1134,7 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>876: source value based on TIU DOCUMENT - PATIENT (8925-.02)</t>
+    <t>876: reference based on TIU DOCUMENT - PATIENT (8925-.02)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.PatientIEN</t>
@@ -1184,10 +1184,7 @@
     <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
   </si>
   <si>
-    <t>877: source value based on TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.EntryDateTime</t>
+    <t>877: transform using Resource_creation_time()</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1205,7 +1202,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>
@@ -1218,7 +1215,7 @@
     <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
   </si>
   <si>
-    <t>1663: source value based on TIU DOCUMENT - SIGNED BY (8925-1502)</t>
+    <t>1663: reference based on TIU DOCUMENT - SIGNED BY (8925-1502)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.SignedByStaffIEN</t>
@@ -1248,46 +1245,46 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+  </si>
+  <si>
+    <t>879: reference based on TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.VerifiedByStaffIEN</t>
+  </si>
+  <si>
+    <t>Composition.attester</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/legalAuthenticator</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>TXA-10</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>DocumentReference.custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>
-    <t>Who/what authenticated the document</t>
-  </si>
-  <si>
-    <t>Which person or organization authenticates that this document is valid.</t>
-  </si>
-  <si>
-    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
-  </si>
-  <si>
-    <t>879: source value based on TIU DOCUMENT - VERIFIED BY (8925-1306)</t>
-  </si>
-  <si>
-    <t>TIU.TIUDocument.VerifiedByStaffIEN</t>
-  </si>
-  <si>
-    <t>Composition.attester</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/legalAuthenticator</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>TXA-10</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>DocumentReference.custodian</t>
-  </si>
-  <si>
     <t>Organization which maintains the document</t>
   </si>
   <si>
@@ -1297,7 +1294,7 @@
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
-    <t>880: source value based on TIU DOCUMENT - DIVISION (8925-1212)</t>
+    <t>880: reference based on TIU DOCUMENT - DIVISION (8925-1212)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.InstitutionIEN</t>
@@ -1777,6 +1774,9 @@
   </si>
   <si>
     <t>896: source value based on TIU DOCUMENT - ENTRY DATE/TIME (8925-1201)</t>
+  </si>
+  <si>
+    <t>TIU.TIUDocument.EntryDateTime</t>
   </si>
   <si>
     <t>DocumentReference.content.format</t>
@@ -2436,7 +2436,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -7472,25 +7472,25 @@
         <v>377</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>83</v>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7527,16 +7527,16 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7586,7 +7586,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>84</v>
@@ -7601,42 +7601,42 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AQ39" t="s" s="2">
+      <c r="AR39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS39" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="AR39" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS39" t="s" s="2">
+      <c r="AT39" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AT39" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7659,16 +7659,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7718,7 +7718,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>84</v>
@@ -7733,42 +7733,42 @@
         <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AQ40" t="s" s="2">
+      <c r="AS40" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AR40" t="s" s="2">
+      <c r="AT40" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AT40" t="s" s="2">
-        <v>409</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7791,16 +7791,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>233</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7850,7 +7850,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -7865,22 +7865,22 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7923,16 +7923,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7982,7 +7982,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -8009,30 +8009,30 @@
         <v>83</v>
       </c>
       <c r="AO42" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT42" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT42" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8159,10 +8159,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8291,14 +8291,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8320,10 +8320,10 @@
         <v>141</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>144</v>
@@ -8378,7 +8378,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>84</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8454,13 +8454,13 @@
         <v>115</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8489,11 +8489,11 @@
         <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8537,30 +8537,30 @@
         <v>83</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT46" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT46" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8583,13 +8583,13 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8640,7 +8640,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>95</v>
@@ -8667,30 +8667,30 @@
         <v>83</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AT47" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AT47" t="s" s="2">
-        <v>449</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8716,16 +8716,16 @@
         <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8774,7 +8774,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>84</v>
@@ -8789,42 +8789,42 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS48" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AQ48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS48" t="s" s="2">
+      <c r="AT48" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AT48" t="s" s="2">
-        <v>460</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8850,16 +8850,16 @@
         <v>196</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8887,11 +8887,11 @@
         <v>201</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>84</v>
@@ -8923,42 +8923,42 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AQ49" t="s" s="2">
+      <c r="AR49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS49" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AR49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS49" t="s" s="2">
+      <c r="AT49" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AT49" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8981,13 +8981,13 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -9038,7 +9038,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>95</v>
@@ -9065,10 +9065,10 @@
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9085,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9183,7 +9183,7 @@
         <v>83</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
@@ -9215,10 +9215,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9347,14 +9347,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9376,10 +9376,10 @@
         <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>144</v>
@@ -9434,7 +9434,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>84</v>
@@ -9481,10 +9481,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9507,13 +9507,13 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9564,7 +9564,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>95</v>
@@ -9576,45 +9576,45 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AK54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AP54" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
+      <c r="AR54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS54" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AR54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS54" t="s" s="2">
+      <c r="AT54" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AT54" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9709,7 +9709,7 @@
         <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9873,10 +9873,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9902,14 +9902,14 @@
         <v>115</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9919,10 +9919,10 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="T57" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -9937,28 +9937,28 @@
         <v>190</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>84</v>
@@ -9973,31 +9973,31 @@
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP57" t="s" s="2">
+      <c r="AQ57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS57" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS57" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="AT57" t="s" s="2">
         <v>83</v>
@@ -10005,10 +10005,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10034,14 +10034,14 @@
         <v>115</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -10054,7 +10054,7 @@
         <v>83</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>83</v>
@@ -10090,7 +10090,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>84</v>
@@ -10105,22 +10105,22 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>83</v>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10163,19 +10163,19 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -10224,7 +10224,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>84</v>
@@ -10233,37 +10233,37 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS59" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AT59" t="s" s="2">
         <v>83</v>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10297,19 +10297,19 @@
         <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -10322,43 +10322,43 @@
         <v>83</v>
       </c>
       <c r="T60" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>84</v>
@@ -10367,37 +10367,37 @@
         <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AL60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AN60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="AQ60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AR60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AS60" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AT60" t="s" s="2">
         <v>83</v>
@@ -10405,10 +10405,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10431,19 +10431,19 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10492,7 +10492,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>84</v>
@@ -10507,22 +10507,22 @@
         <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>83</v>
@@ -10539,10 +10539,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10565,19 +10565,19 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10626,7 +10626,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>84</v>
@@ -10641,22 +10641,22 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>83</v>
@@ -10673,10 +10673,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10702,14 +10702,14 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10722,43 +10722,43 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -10773,7 +10773,7 @@
         <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>267</v>
@@ -10788,7 +10788,7 @@
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>83</v>
@@ -10805,10 +10805,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10831,17 +10831,17 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10890,7 +10890,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>84</v>
@@ -10905,11 +10905,11 @@
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AM64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>83</v>
@@ -11050,7 +11050,7 @@
         <v>576</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>577</v>
@@ -11093,7 +11093,7 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>580</v>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11490,10 +11490,10 @@
         <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>144</v>
@@ -11548,7 +11548,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>84</v>
@@ -12275,7 +12275,7 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>620</v>
@@ -12407,7 +12407,7 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>630</v>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1134,7 +1134,7 @@
     <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
   </si>
   <si>
-    <t>876: reference based on TIU DOCUMENT - PATIENT (8925-.02)</t>
+    <t>876: reference based on TIU DOCUMENT - PATIENT &gt; PATIENT/IHS - NAME (8925-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>TIU.TIUDocument.PatientIEN</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceDocumentReference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
